--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135313304</v>
+        <v>135356799</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655408</v>
+        <v>655382</v>
       </c>
       <c r="R2" t="n">
-        <v>7331025</v>
+        <v>7331044</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +770,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135313461</v>
+        <v>135356794</v>
       </c>
       <c r="B3" t="n">
         <v>79452</v>
@@ -808,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655548</v>
+        <v>655301</v>
       </c>
       <c r="R3" t="n">
-        <v>7330875</v>
+        <v>7330978</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,84 +877,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135313467</v>
+        <v>135356802</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655548</v>
+        <v>655379</v>
       </c>
       <c r="R4" t="n">
-        <v>7330875</v>
+        <v>7331065</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +992,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135313442</v>
+        <v>135356803</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>79452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,42 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655548</v>
+        <v>655406</v>
       </c>
       <c r="R5" t="n">
-        <v>7330875</v>
+        <v>7331087</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1073,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,15 +1103,1991 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135356789</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>655329</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7330923</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135356791</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>655322</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7330929</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135356793</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>655300</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7330952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135356798</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>655361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7331049</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135356801</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7331066</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135356804</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>655404</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7331113</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135356805</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>655407</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7331128</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135356806</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>655347</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7331089</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135356807</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>655326</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7331044</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135356808</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>655319</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7331005</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135356790</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>655331</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7330925</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135356797</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>655353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7331030</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135356800</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7331068</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135313304</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>655408</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7331025</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135356795</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>655319</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7330993</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135313461</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>864</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135313467</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135313442</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,32 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135356789</v>
+        <v>135358259</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655329</v>
+        <v>655302</v>
       </c>
       <c r="R6" t="n">
-        <v>7330923</v>
+        <v>7331003</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,19 +1187,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1204,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1230,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135356791</v>
+        <v>135356789</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1265,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655322</v>
+        <v>655329</v>
       </c>
       <c r="R7" t="n">
-        <v>7330929</v>
+        <v>7330923</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135356793</v>
+        <v>135356791</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1376,13 +1366,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655300</v>
+        <v>655322</v>
       </c>
       <c r="R8" t="n">
-        <v>7330952</v>
+        <v>7330929</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135356798</v>
+        <v>135356793</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1487,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655361</v>
+        <v>655300</v>
       </c>
       <c r="R9" t="n">
-        <v>7331049</v>
+        <v>7330952</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135356801</v>
+        <v>135356798</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1598,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655378</v>
+        <v>655361</v>
       </c>
       <c r="R10" t="n">
-        <v>7331066</v>
+        <v>7331049</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135356804</v>
+        <v>135356801</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1709,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655404</v>
+        <v>655378</v>
       </c>
       <c r="R11" t="n">
-        <v>7331113</v>
+        <v>7331066</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135356805</v>
+        <v>135356804</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1820,13 +1810,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655407</v>
+        <v>655404</v>
       </c>
       <c r="R12" t="n">
-        <v>7331128</v>
+        <v>7331113</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,7 +1886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135356806</v>
+        <v>135356805</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1931,13 +1921,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655347</v>
+        <v>655407</v>
       </c>
       <c r="R13" t="n">
-        <v>7331089</v>
+        <v>7331128</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,7 +1997,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135356807</v>
+        <v>135356806</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -2042,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655326</v>
+        <v>655347</v>
       </c>
       <c r="R14" t="n">
-        <v>7331044</v>
+        <v>7331089</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,7 +2108,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135356808</v>
+        <v>135356807</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655319</v>
+        <v>655326</v>
       </c>
       <c r="R15" t="n">
-        <v>7331005</v>
+        <v>7331044</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2188,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,32 +2219,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135356790</v>
+        <v>135356808</v>
       </c>
       <c r="B16" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655331</v>
+        <v>655319</v>
       </c>
       <c r="R16" t="n">
-        <v>7330925</v>
+        <v>7331005</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,7 +2289,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2309,7 +2299,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,32 +2330,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135356797</v>
+        <v>135358263</v>
       </c>
       <c r="B17" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,13 +2365,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655353</v>
+        <v>655411</v>
       </c>
       <c r="R17" t="n">
-        <v>7331030</v>
+        <v>7331023</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,19 +2398,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,12 +2415,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2451,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135356800</v>
+        <v>135356790</v>
       </c>
       <c r="B18" t="n">
         <v>83358</v>
@@ -2486,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655378</v>
+        <v>655331</v>
       </c>
       <c r="R18" t="n">
-        <v>7331068</v>
+        <v>7330925</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2521,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135313304</v>
+        <v>135356797</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,42 +2553,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655408</v>
+        <v>655353</v>
       </c>
       <c r="R19" t="n">
-        <v>7331025</v>
+        <v>7331030</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,12 +2607,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,44 +2637,48 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135356795</v>
+        <v>135356800</v>
       </c>
       <c r="B20" t="n">
-        <v>5201</v>
+        <v>83358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655319</v>
+        <v>655378</v>
       </c>
       <c r="R20" t="n">
-        <v>7330993</v>
+        <v>7331068</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2734,7 +2723,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2744,7 +2733,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135313461</v>
+        <v>135313304</v>
       </c>
       <c r="B21" t="n">
-        <v>79452</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,34 +2775,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655548</v>
+        <v>655408</v>
       </c>
       <c r="R21" t="n">
-        <v>7330875</v>
+        <v>7331025</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,26 +2850,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2892,48 +2866,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135313467</v>
+        <v>135358260</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655548</v>
+        <v>655305</v>
       </c>
       <c r="R22" t="n">
-        <v>7330875</v>
+        <v>7331010</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,12 +2931,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,39 +2956,43 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135313442</v>
+        <v>135356795</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>5201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3018,24 +3001,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655548</v>
+        <v>655319</v>
       </c>
       <c r="R23" t="n">
-        <v>7330875</v>
+        <v>7330993</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,12 +3037,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,15 +3067,638 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135358261</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>655366</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7331190</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135313461</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>864</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135358264</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>864</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>655581</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7330768</v>
+      </c>
+      <c r="S26" t="n">
+        <v>31</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135313467</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135358262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>655425</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7331045</v>
+      </c>
+      <c r="S28" t="n">
+        <v>12</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135313442</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,32 +2431,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135356790</v>
+        <v>135359086</v>
       </c>
       <c r="B18" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655331</v>
+        <v>655340</v>
       </c>
       <c r="R18" t="n">
-        <v>7330925</v>
+        <v>7330935</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2511,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,12 +2531,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2542,32 +2547,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135356797</v>
+        <v>135359087</v>
       </c>
       <c r="B19" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2577,13 +2582,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655353</v>
+        <v>655331</v>
       </c>
       <c r="R19" t="n">
-        <v>7331030</v>
+        <v>7330948</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2627,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,12 +2647,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2653,32 +2663,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135356800</v>
+        <v>135359088</v>
       </c>
       <c r="B20" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2688,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655378</v>
+        <v>655323</v>
       </c>
       <c r="R20" t="n">
-        <v>7331068</v>
+        <v>7330955</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2733,7 +2743,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,12 +2763,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2764,53 +2779,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135313304</v>
+        <v>135359089</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655408</v>
+        <v>655319</v>
       </c>
       <c r="R21" t="n">
-        <v>7331025</v>
+        <v>7330980</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2834,12 +2844,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,44 +2879,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135358260</v>
+        <v>135359090</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655305</v>
+        <v>655314</v>
       </c>
       <c r="R22" t="n">
-        <v>7331010</v>
+        <v>7330980</v>
       </c>
       <c r="S22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2934,14 +2963,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2956,12 +2995,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2972,32 +3011,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135356795</v>
+        <v>135359091</v>
       </c>
       <c r="B23" t="n">
-        <v>5201</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3007,13 +3046,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655319</v>
+        <v>655343</v>
       </c>
       <c r="R23" t="n">
-        <v>7330993</v>
+        <v>7330985</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3042,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +3091,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3083,7 +3127,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135358261</v>
+        <v>135359092</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3118,13 +3162,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655366</v>
+        <v>655349</v>
       </c>
       <c r="R24" t="n">
-        <v>7331190</v>
+        <v>7331023</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3151,9 +3195,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran. Mycket förekomst.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,12 +3227,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3184,48 +3243,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135313461</v>
+        <v>135359093</v>
       </c>
       <c r="B25" t="n">
-        <v>79452</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655548</v>
+        <v>655349</v>
       </c>
       <c r="R25" t="n">
-        <v>7330875</v>
+        <v>7331028</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3249,12 +3308,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,68 +3339,52 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135358264</v>
+        <v>135359095</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3336,13 +3394,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655581</v>
+        <v>655360</v>
       </c>
       <c r="R26" t="n">
-        <v>7330768</v>
+        <v>7331083</v>
       </c>
       <c r="S26" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3369,9 +3427,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,12 +3459,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3402,7 +3475,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135313467</v>
+        <v>135359097</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3433,17 +3506,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655548</v>
+        <v>655379</v>
       </c>
       <c r="R27" t="n">
-        <v>7330875</v>
+        <v>7331136</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,12 +3540,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal död tall med stamspricka.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,44 +3575,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135358262</v>
+        <v>135356790</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,13 +3626,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655425</v>
+        <v>655331</v>
       </c>
       <c r="R28" t="n">
-        <v>7331045</v>
+        <v>7330925</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3567,9 +3659,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,12 +3686,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3600,10 +3702,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135313442</v>
+        <v>135356797</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3611,42 +3713,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655548</v>
+        <v>655353</v>
       </c>
       <c r="R29" t="n">
-        <v>7330875</v>
+        <v>7331030</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3670,12 +3767,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,15 +3797,1764 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135356800</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7331068</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135359085</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>655331</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7330912</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135359098</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>655351</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7331128</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På rötterna på mycket gammal torr tallåga.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135359096</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>655395</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7331098</v>
+      </c>
+      <c r="S33" t="n">
+        <v>23</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hål efter spillkråka i torraka av tall.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135313304</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>655408</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7331025</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135358260</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655305</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7331010</v>
+      </c>
+      <c r="S35" t="n">
+        <v>22</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135359094</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>655359</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7331092</v>
+      </c>
+      <c r="S36" t="n">
+        <v>32</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färskt spår och äldre spår av tretåig hackspett på gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135359100</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>655337</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7331075</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Många spår av ringhack med kådutfällning från tretåig hackspett. Runt hela granen.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135359099</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>655346</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7331111</v>
+      </c>
+      <c r="S38" t="n">
+        <v>18</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135356795</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655319</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7330993</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135358261</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655366</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7331190</v>
+      </c>
+      <c r="S40" t="n">
+        <v>9</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135313461</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>864</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135358264</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>864</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>655581</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7330768</v>
+      </c>
+      <c r="S42" t="n">
+        <v>31</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135313467</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135358262</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>655425</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7331045</v>
+      </c>
+      <c r="S44" t="n">
+        <v>12</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135313442</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135356799</v>
+        <v>135357390</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655382</v>
+        <v>655334</v>
       </c>
       <c r="R2" t="n">
-        <v>7331044</v>
+        <v>7330928</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135356794</v>
+        <v>135356799</v>
       </c>
       <c r="B3" t="n">
-        <v>79452</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655301</v>
+        <v>655382</v>
       </c>
       <c r="R3" t="n">
-        <v>7330978</v>
+        <v>7331044</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135356802</v>
+        <v>135356794</v>
       </c>
       <c r="B4" t="n">
         <v>79452</v>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655379</v>
+        <v>655301</v>
       </c>
       <c r="R4" t="n">
-        <v>7331065</v>
+        <v>7330978</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135356803</v>
+        <v>135356802</v>
       </c>
       <c r="B5" t="n">
         <v>79452</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655406</v>
+        <v>655379</v>
       </c>
       <c r="R5" t="n">
-        <v>7331087</v>
+        <v>7331065</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135358259</v>
+        <v>135356803</v>
       </c>
       <c r="B6" t="n">
         <v>79452</v>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655302</v>
+        <v>655406</v>
       </c>
       <c r="R6" t="n">
-        <v>7331003</v>
+        <v>7331087</v>
       </c>
       <c r="S6" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,9 +1187,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1220,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135356789</v>
+        <v>135358259</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655329</v>
+        <v>655302</v>
       </c>
       <c r="R7" t="n">
-        <v>7330923</v>
+        <v>7331003</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1298,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1331,32 +1331,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135356791</v>
+        <v>135357389</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655322</v>
+        <v>655303</v>
       </c>
       <c r="R8" t="n">
-        <v>7330929</v>
+        <v>7330924</v>
       </c>
       <c r="S8" t="n">
         <v>14</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,12 +1426,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135356793</v>
+        <v>135356789</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655300</v>
+        <v>655329</v>
       </c>
       <c r="R9" t="n">
-        <v>7330952</v>
+        <v>7330923</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135356798</v>
+        <v>135356791</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655361</v>
+        <v>655322</v>
       </c>
       <c r="R10" t="n">
-        <v>7331049</v>
+        <v>7330929</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135356801</v>
+        <v>135356793</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655378</v>
+        <v>655300</v>
       </c>
       <c r="R11" t="n">
-        <v>7331066</v>
+        <v>7330952</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135356804</v>
+        <v>135356798</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655404</v>
+        <v>655361</v>
       </c>
       <c r="R12" t="n">
-        <v>7331113</v>
+        <v>7331049</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,7 +1886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135356805</v>
+        <v>135356801</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655407</v>
+        <v>655378</v>
       </c>
       <c r="R13" t="n">
-        <v>7331128</v>
+        <v>7331066</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +1997,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135356806</v>
+        <v>135356804</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655347</v>
+        <v>655404</v>
       </c>
       <c r="R14" t="n">
-        <v>7331089</v>
+        <v>7331113</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135356807</v>
+        <v>135356805</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655326</v>
+        <v>655407</v>
       </c>
       <c r="R15" t="n">
-        <v>7331044</v>
+        <v>7331128</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,7 +2219,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135356808</v>
+        <v>135356806</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655319</v>
+        <v>655347</v>
       </c>
       <c r="R16" t="n">
-        <v>7331005</v>
+        <v>7331089</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135358263</v>
+        <v>135356807</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655411</v>
+        <v>655326</v>
       </c>
       <c r="R17" t="n">
-        <v>7331023</v>
+        <v>7331044</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,9 +2398,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,12 +2425,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2431,7 +2441,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135359086</v>
+        <v>135356808</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2466,13 +2476,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655340</v>
+        <v>655319</v>
       </c>
       <c r="R18" t="n">
-        <v>7330935</v>
+        <v>7331005</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2501,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,12 +2521,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,12 +2536,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2547,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135359087</v>
+        <v>135357388</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2582,13 +2587,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655331</v>
+        <v>655277</v>
       </c>
       <c r="R19" t="n">
-        <v>7330948</v>
+        <v>7330921</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,7 +2622,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,12 +2632,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tvåstammig gran.</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,12 +2647,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2663,7 +2663,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135359088</v>
+        <v>135357392</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655323</v>
+        <v>655367</v>
       </c>
       <c r="R20" t="n">
-        <v>7330955</v>
+        <v>7330852</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,12 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,12 +2758,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2779,7 +2774,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135359089</v>
+        <v>135357394</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2814,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655319</v>
+        <v>655416</v>
       </c>
       <c r="R21" t="n">
-        <v>7330980</v>
+        <v>7330850</v>
       </c>
       <c r="S21" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2844,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,12 +2854,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På större gran.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,12 +2869,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2895,7 +2885,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135359090</v>
+        <v>135358263</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2930,13 +2920,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655314</v>
+        <v>655411</v>
       </c>
       <c r="R22" t="n">
-        <v>7330980</v>
+        <v>7331023</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2963,24 +2953,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,12 +2970,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3011,7 +2986,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135359091</v>
+        <v>135359086</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -3046,13 +3021,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655343</v>
+        <v>655340</v>
       </c>
       <c r="R23" t="n">
-        <v>7330985</v>
+        <v>7330935</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3056,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,12 +3066,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På större gran.</t>
+          <t>På äldre gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,7 +3102,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135359092</v>
+        <v>135359087</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3162,13 +3137,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655349</v>
+        <v>655331</v>
       </c>
       <c r="R24" t="n">
-        <v>7331023</v>
+        <v>7330948</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3197,7 +3172,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,12 +3182,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran. Mycket förekomst.</t>
+          <t>På tvåstammig gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,7 +3218,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135359093</v>
+        <v>135359088</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3278,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655349</v>
+        <v>655323</v>
       </c>
       <c r="R25" t="n">
-        <v>7331028</v>
+        <v>7330955</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3313,7 +3288,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3323,12 +3298,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På större gran.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,7 +3334,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135359095</v>
+        <v>135359089</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3394,13 +3369,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655360</v>
+        <v>655319</v>
       </c>
       <c r="R26" t="n">
-        <v>7331083</v>
+        <v>7330980</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3429,7 +3404,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3439,12 +3414,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135359097</v>
+        <v>135359090</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3510,13 +3485,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655379</v>
+        <v>655314</v>
       </c>
       <c r="R27" t="n">
-        <v>7331136</v>
+        <v>7330980</v>
       </c>
       <c r="S27" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3545,7 +3520,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3555,12 +3530,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal död tall med stamspricka.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,32 +3566,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135356790</v>
+        <v>135359091</v>
       </c>
       <c r="B28" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,13 +3601,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655331</v>
+        <v>655343</v>
       </c>
       <c r="R28" t="n">
-        <v>7330925</v>
+        <v>7330985</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,7 +3646,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,12 +3666,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3702,32 +3682,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135356797</v>
+        <v>135359092</v>
       </c>
       <c r="B29" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3737,13 +3717,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655353</v>
+        <v>655349</v>
       </c>
       <c r="R29" t="n">
-        <v>7331030</v>
+        <v>7331023</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3782,7 +3762,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran. Mycket förekomst.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,12 +3782,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3813,32 +3798,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135356800</v>
+        <v>135359093</v>
       </c>
       <c r="B30" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3848,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655378</v>
+        <v>655349</v>
       </c>
       <c r="R30" t="n">
-        <v>7331068</v>
+        <v>7331028</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3868,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3893,7 +3878,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,12 +3898,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3924,32 +3914,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135359085</v>
+        <v>135359095</v>
       </c>
       <c r="B31" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3959,13 +3949,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655331</v>
+        <v>655360</v>
       </c>
       <c r="R31" t="n">
-        <v>7330912</v>
+        <v>7331083</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3994,7 +3984,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4004,12 +3994,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På större gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,32 +4030,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135359098</v>
+        <v>135359097</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,13 +4065,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655351</v>
+        <v>655379</v>
       </c>
       <c r="R32" t="n">
-        <v>7331128</v>
+        <v>7331136</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,12 +4110,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På rötterna på mycket gammal torr tallåga.</t>
+          <t>På gammal död tall med stamspricka.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,32 +4146,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135359096</v>
+        <v>135356790</v>
       </c>
       <c r="B33" t="n">
-        <v>57972</v>
+        <v>83358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4191,13 +4181,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655395</v>
+        <v>655331</v>
       </c>
       <c r="R33" t="n">
-        <v>7331098</v>
+        <v>7330925</v>
       </c>
       <c r="S33" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4226,7 +4216,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,12 +4226,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hål efter spillkråka i torraka av tall.</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,12 +4241,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4272,10 +4257,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135313304</v>
+        <v>135356797</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4283,42 +4268,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655408</v>
+        <v>655353</v>
       </c>
       <c r="R34" t="n">
-        <v>7331025</v>
+        <v>7331030</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4342,12 +4322,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,22 +4352,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Jennica Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135358260</v>
+        <v>135356800</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,21 +4379,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4409,13 +4403,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655305</v>
+        <v>655378</v>
       </c>
       <c r="R35" t="n">
-        <v>7331010</v>
+        <v>7331068</v>
       </c>
       <c r="S35" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,14 +4436,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,12 +4463,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4480,10 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135359094</v>
+        <v>135359085</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4491,21 +4490,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,13 +4514,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655359</v>
+        <v>655331</v>
       </c>
       <c r="R36" t="n">
-        <v>7331092</v>
+        <v>7330912</v>
       </c>
       <c r="S36" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4560,12 +4559,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färskt spår och äldre spår av tretåig hackspett på gammal gran.</t>
+          <t>På större gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4596,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135359100</v>
+        <v>135359098</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4607,21 +4606,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4631,13 +4630,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655337</v>
+        <v>655351</v>
       </c>
       <c r="R37" t="n">
-        <v>7331075</v>
+        <v>7331128</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4666,7 +4665,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4676,12 +4675,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Många spår av ringhack med kådutfällning från tretåig hackspett. Runt hela granen.</t>
+          <t>På rötterna på mycket gammal torr tallåga.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135359099</v>
+        <v>135359096</v>
       </c>
       <c r="B38" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,21 +4722,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4747,13 +4746,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655346</v>
+        <v>655395</v>
       </c>
       <c r="R38" t="n">
-        <v>7331111</v>
+        <v>7331098</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,7 +4781,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,12 +4791,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
+          <t>Hål efter spillkråka i torraka av tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,27 +4827,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135356795</v>
+        <v>135313304</v>
       </c>
       <c r="B39" t="n">
-        <v>5201</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4857,19 +4856,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655319</v>
+        <v>655408</v>
       </c>
       <c r="R39" t="n">
-        <v>7330993</v>
+        <v>7331025</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4893,22 +4897,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,48 +4917,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135358261</v>
+        <v>135358260</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4974,13 +4964,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655366</v>
+        <v>655305</v>
       </c>
       <c r="R40" t="n">
-        <v>7331190</v>
+        <v>7331010</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5010,6 +5000,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5040,10 +5035,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135313461</v>
+        <v>135359094</v>
       </c>
       <c r="B41" t="n">
-        <v>79452</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5051,37 +5046,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655548</v>
+        <v>655359</v>
       </c>
       <c r="R41" t="n">
-        <v>7330875</v>
+        <v>7331092</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5105,12 +5100,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt spår och äldre spår av tretåig hackspett på gammal gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5121,46 +5131,30 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135358264</v>
+        <v>135359100</v>
       </c>
       <c r="B42" t="n">
-        <v>79452</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5168,21 +5162,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5192,13 +5186,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655581</v>
+        <v>655337</v>
       </c>
       <c r="R42" t="n">
-        <v>7330768</v>
+        <v>7331075</v>
       </c>
       <c r="S42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5225,9 +5219,24 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Många spår av ringhack med kådutfällning från tretåig hackspett. Runt hela granen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5242,12 +5251,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5258,48 +5267,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135313467</v>
+        <v>135359099</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655548</v>
+        <v>655346</v>
       </c>
       <c r="R43" t="n">
-        <v>7330875</v>
+        <v>7331111</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5323,12 +5332,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,44 +5367,48 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Maja Josefsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135358262</v>
+        <v>135356795</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>5201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5390,13 +5418,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655425</v>
+        <v>655319</v>
       </c>
       <c r="R44" t="n">
-        <v>7331045</v>
+        <v>7330993</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5423,9 +5451,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5440,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5456,53 +5494,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135313442</v>
+        <v>135358261</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655548</v>
+        <v>655366</v>
       </c>
       <c r="R45" t="n">
-        <v>7330875</v>
+        <v>7331190</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5526,12 +5559,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5546,15 +5579,1986 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135313461</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>864</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135358264</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>864</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>655581</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7330768</v>
+      </c>
+      <c r="S47" t="n">
+        <v>31</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135357396</v>
+      </c>
+      <c r="B48" t="n">
+        <v>83363</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>655579</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7330863</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135313467</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135357404</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>655735</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7330853</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135358262</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>655425</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7331045</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135313442</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>655548</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7330875</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135357407</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>655446</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7330950</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135357398</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>655579</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7330863</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135357400</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>655621</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7330834</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135357395</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>655546</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7330858</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135357397</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>655579</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7330863</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135357399</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>655621</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7330834</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135357401</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>655806</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7330742</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135357402</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>655842</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7330740</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135357403</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>655735</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7330853</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135357405</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>655649</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7330872</v>
+      </c>
+      <c r="S62" t="n">
+        <v>11</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135357406</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>655448</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7330951</v>
+      </c>
+      <c r="S63" t="n">
+        <v>12</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -6864,7 +6864,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY253"/>
+  <dimension ref="A1:AY254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17723,10 +17723,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135313467</v>
+        <v>135388328</v>
       </c>
       <c r="B154" t="n">
-        <v>79373</v>
+        <v>92320</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17734,37 +17734,40 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>655548</v>
+        <v>655426</v>
       </c>
       <c r="R154" t="n">
-        <v>7330875</v>
+        <v>7330863</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17788,12 +17791,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17802,25 +17815,30 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY154" t="inlineStr"/>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357404</v>
+        <v>135313467</v>
       </c>
       <c r="B155" t="n">
         <v>79373</v>
@@ -17851,17 +17869,17 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>655735</v>
+        <v>655548</v>
       </c>
       <c r="R155" t="n">
-        <v>7330853</v>
+        <v>7330875</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17885,22 +17903,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17915,23 +17923,19 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357620</v>
+        <v>135357404</v>
       </c>
       <c r="B156" t="n">
         <v>79373</v>
@@ -17966,10 +17970,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>655434</v>
+        <v>655735</v>
       </c>
       <c r="R156" t="n">
-        <v>7331068</v>
+        <v>7330853</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18001,7 +18005,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18011,7 +18015,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18026,12 +18030,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -18042,7 +18046,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357621</v>
+        <v>135357620</v>
       </c>
       <c r="B157" t="n">
         <v>79373</v>
@@ -18077,10 +18081,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>655422</v>
+        <v>655434</v>
       </c>
       <c r="R157" t="n">
-        <v>7331047</v>
+        <v>7331068</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18112,7 +18116,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18122,7 +18126,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18153,7 +18157,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357736</v>
+        <v>135357621</v>
       </c>
       <c r="B158" t="n">
         <v>79373</v>
@@ -18184,14 +18188,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>655499</v>
+        <v>655422</v>
       </c>
       <c r="R158" t="n">
-        <v>7330814</v>
+        <v>7331047</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18223,7 +18227,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18233,7 +18237,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18248,12 +18252,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -18264,7 +18268,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135357737</v>
+        <v>135357736</v>
       </c>
       <c r="B159" t="n">
         <v>79373</v>
@@ -18299,13 +18303,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>655585</v>
+        <v>655499</v>
       </c>
       <c r="R159" t="n">
-        <v>7330827</v>
+        <v>7330814</v>
       </c>
       <c r="S159" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18334,7 +18338,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18344,7 +18348,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18375,7 +18379,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135357740</v>
+        <v>135357737</v>
       </c>
       <c r="B160" t="n">
         <v>79373</v>
@@ -18410,13 +18414,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>655599</v>
+        <v>655585</v>
       </c>
       <c r="R160" t="n">
-        <v>7330842</v>
+        <v>7330827</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18445,7 +18449,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18455,7 +18459,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18486,7 +18490,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135357750</v>
+        <v>135357740</v>
       </c>
       <c r="B161" t="n">
         <v>79373</v>
@@ -18521,10 +18525,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>655648</v>
+        <v>655599</v>
       </c>
       <c r="R161" t="n">
-        <v>7330944</v>
+        <v>7330842</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18556,7 +18560,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18566,7 +18570,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18597,7 +18601,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135357858</v>
+        <v>135357750</v>
       </c>
       <c r="B162" t="n">
         <v>79373</v>
@@ -18628,17 +18632,17 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>655422</v>
+        <v>655648</v>
       </c>
       <c r="R162" t="n">
-        <v>7330878</v>
+        <v>7330944</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18667,7 +18671,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18677,7 +18681,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18692,19 +18696,23 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135357866</v>
+        <v>135357858</v>
       </c>
       <c r="B163" t="n">
         <v>79373</v>
@@ -18739,10 +18747,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>655484</v>
+        <v>655422</v>
       </c>
       <c r="R163" t="n">
-        <v>7330859</v>
+        <v>7330878</v>
       </c>
       <c r="S163" t="n">
         <v>3</v>
@@ -18774,7 +18782,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18784,12 +18792,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18816,7 +18819,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135357867</v>
+        <v>135357866</v>
       </c>
       <c r="B164" t="n">
         <v>79373</v>
@@ -18851,10 +18854,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>655503</v>
+        <v>655484</v>
       </c>
       <c r="R164" t="n">
-        <v>7330869</v>
+        <v>7330859</v>
       </c>
       <c r="S164" t="n">
         <v>3</v>
@@ -18886,7 +18889,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18896,7 +18899,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -18928,7 +18931,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135357872</v>
+        <v>135357867</v>
       </c>
       <c r="B165" t="n">
         <v>79373</v>
@@ -18963,10 +18966,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>655555</v>
+        <v>655503</v>
       </c>
       <c r="R165" t="n">
-        <v>7330879</v>
+        <v>7330869</v>
       </c>
       <c r="S165" t="n">
         <v>3</v>
@@ -18998,7 +19001,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19008,7 +19011,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19035,7 +19043,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135357878</v>
+        <v>135357872</v>
       </c>
       <c r="B166" t="n">
         <v>79373</v>
@@ -19070,10 +19078,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>655566</v>
+        <v>655555</v>
       </c>
       <c r="R166" t="n">
-        <v>7330892</v>
+        <v>7330879</v>
       </c>
       <c r="S166" t="n">
         <v>3</v>
@@ -19105,7 +19113,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19115,7 +19123,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19142,7 +19150,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135357883</v>
+        <v>135357878</v>
       </c>
       <c r="B167" t="n">
         <v>79373</v>
@@ -19177,10 +19185,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>655585</v>
+        <v>655566</v>
       </c>
       <c r="R167" t="n">
-        <v>7330843</v>
+        <v>7330892</v>
       </c>
       <c r="S167" t="n">
         <v>3</v>
@@ -19212,7 +19220,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19222,7 +19230,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19249,7 +19257,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135357896</v>
+        <v>135357883</v>
       </c>
       <c r="B168" t="n">
         <v>79373</v>
@@ -19284,10 +19292,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>655823</v>
+        <v>655585</v>
       </c>
       <c r="R168" t="n">
-        <v>7330749</v>
+        <v>7330843</v>
       </c>
       <c r="S168" t="n">
         <v>3</v>
@@ -19319,7 +19327,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19329,7 +19337,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19356,7 +19364,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135357897</v>
+        <v>135357896</v>
       </c>
       <c r="B169" t="n">
         <v>79373</v>
@@ -19391,10 +19399,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>655886</v>
+        <v>655823</v>
       </c>
       <c r="R169" t="n">
-        <v>7330755</v>
+        <v>7330749</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -19426,7 +19434,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19436,7 +19444,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19463,7 +19471,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>135357899</v>
+        <v>135357897</v>
       </c>
       <c r="B170" t="n">
         <v>79373</v>
@@ -19498,10 +19506,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>655753</v>
+        <v>655886</v>
       </c>
       <c r="R170" t="n">
-        <v>7330807</v>
+        <v>7330755</v>
       </c>
       <c r="S170" t="n">
         <v>3</v>
@@ -19533,7 +19541,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19543,7 +19551,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19570,7 +19578,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>135357900</v>
+        <v>135357899</v>
       </c>
       <c r="B171" t="n">
         <v>79373</v>
@@ -19605,10 +19613,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>655702</v>
+        <v>655753</v>
       </c>
       <c r="R171" t="n">
-        <v>7330809</v>
+        <v>7330807</v>
       </c>
       <c r="S171" t="n">
         <v>3</v>
@@ -19640,7 +19648,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19650,7 +19658,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19677,7 +19685,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>135357901</v>
+        <v>135357900</v>
       </c>
       <c r="B172" t="n">
         <v>79373</v>
@@ -19712,10 +19720,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>655649</v>
+        <v>655702</v>
       </c>
       <c r="R172" t="n">
-        <v>7330880</v>
+        <v>7330809</v>
       </c>
       <c r="S172" t="n">
         <v>3</v>
@@ -19747,7 +19755,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19757,7 +19765,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19784,7 +19792,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>135358262</v>
+        <v>135357901</v>
       </c>
       <c r="B173" t="n">
         <v>79373</v>
@@ -19819,13 +19827,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>655425</v>
+        <v>655649</v>
       </c>
       <c r="R173" t="n">
-        <v>7331045</v>
+        <v>7330880</v>
       </c>
       <c r="S173" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19852,9 +19860,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19869,23 +19887,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>135359801</v>
+        <v>135358262</v>
       </c>
       <c r="B174" t="n">
         <v>79373</v>
@@ -19920,13 +19934,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>655441</v>
+        <v>655425</v>
       </c>
       <c r="R174" t="n">
-        <v>7330837</v>
+        <v>7331045</v>
       </c>
       <c r="S174" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19953,19 +19967,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19980,12 +19984,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -19996,7 +20000,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>135359804</v>
+        <v>135359801</v>
       </c>
       <c r="B175" t="n">
         <v>79373</v>
@@ -20031,13 +20035,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>655451</v>
+        <v>655441</v>
       </c>
       <c r="R175" t="n">
-        <v>7330843</v>
+        <v>7330837</v>
       </c>
       <c r="S175" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20066,7 +20070,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20076,7 +20080,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20107,7 +20111,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135359805</v>
+        <v>135359804</v>
       </c>
       <c r="B176" t="n">
         <v>79373</v>
@@ -20142,13 +20146,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>655464</v>
+        <v>655451</v>
       </c>
       <c r="R176" t="n">
-        <v>7330834</v>
+        <v>7330843</v>
       </c>
       <c r="S176" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20177,7 +20181,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20187,7 +20191,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20218,7 +20222,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>135359809</v>
+        <v>135359805</v>
       </c>
       <c r="B177" t="n">
         <v>79373</v>
@@ -20253,10 +20257,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>655514</v>
+        <v>655464</v>
       </c>
       <c r="R177" t="n">
-        <v>7330831</v>
+        <v>7330834</v>
       </c>
       <c r="S177" t="n">
         <v>5</v>
@@ -20288,7 +20292,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20298,7 +20302,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20329,7 +20333,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>135359810</v>
+        <v>135359809</v>
       </c>
       <c r="B178" t="n">
         <v>79373</v>
@@ -20364,10 +20368,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>655548</v>
+        <v>655514</v>
       </c>
       <c r="R178" t="n">
-        <v>7330834</v>
+        <v>7330831</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20399,7 +20403,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20409,7 +20413,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20440,7 +20444,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135359816</v>
+        <v>135359810</v>
       </c>
       <c r="B179" t="n">
         <v>79373</v>
@@ -20475,13 +20479,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>655579</v>
+        <v>655548</v>
       </c>
       <c r="R179" t="n">
-        <v>7330851</v>
+        <v>7330834</v>
       </c>
       <c r="S179" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20510,7 +20514,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20520,7 +20524,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20551,7 +20555,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>135359818</v>
+        <v>135359816</v>
       </c>
       <c r="B180" t="n">
         <v>79373</v>
@@ -20586,13 +20590,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>655591</v>
+        <v>655579</v>
       </c>
       <c r="R180" t="n">
-        <v>7330837</v>
+        <v>7330851</v>
       </c>
       <c r="S180" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20621,7 +20625,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20631,7 +20635,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20662,7 +20666,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>135359823</v>
+        <v>135359818</v>
       </c>
       <c r="B181" t="n">
         <v>79373</v>
@@ -20697,13 +20701,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>655633</v>
+        <v>655591</v>
       </c>
       <c r="R181" t="n">
-        <v>7330807</v>
+        <v>7330837</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20732,7 +20736,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20742,7 +20746,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20773,7 +20777,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>135359829</v>
+        <v>135359823</v>
       </c>
       <c r="B182" t="n">
         <v>79373</v>
@@ -20808,13 +20812,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>655798</v>
+        <v>655633</v>
       </c>
       <c r="R182" t="n">
-        <v>7330738</v>
+        <v>7330807</v>
       </c>
       <c r="S182" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20843,7 +20847,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20853,7 +20857,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20884,7 +20888,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>135359832</v>
+        <v>135359829</v>
       </c>
       <c r="B183" t="n">
         <v>79373</v>
@@ -20919,13 +20923,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>655909</v>
+        <v>655798</v>
       </c>
       <c r="R183" t="n">
-        <v>7330765</v>
+        <v>7330738</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20954,7 +20958,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20964,7 +20968,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20995,7 +20999,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>135359837</v>
+        <v>135359832</v>
       </c>
       <c r="B184" t="n">
         <v>79373</v>
@@ -21030,13 +21034,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>655782</v>
+        <v>655909</v>
       </c>
       <c r="R184" t="n">
-        <v>7330802</v>
+        <v>7330765</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21065,7 +21069,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21075,7 +21079,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21106,7 +21110,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>135359849</v>
+        <v>135359837</v>
       </c>
       <c r="B185" t="n">
         <v>79373</v>
@@ -21141,10 +21145,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>655661</v>
+        <v>655782</v>
       </c>
       <c r="R185" t="n">
-        <v>7330860</v>
+        <v>7330802</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21176,7 +21180,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21186,7 +21190,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21217,7 +21221,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135362058</v>
+        <v>135359849</v>
       </c>
       <c r="B186" t="n">
         <v>79373</v>
@@ -21252,13 +21256,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>655622</v>
+        <v>655661</v>
       </c>
       <c r="R186" t="n">
-        <v>7331046</v>
+        <v>7330860</v>
       </c>
       <c r="S186" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21287,7 +21291,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21297,7 +21301,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21312,12 +21316,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -21328,7 +21332,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135362062</v>
+        <v>135362058</v>
       </c>
       <c r="B187" t="n">
         <v>79373</v>
@@ -21363,13 +21367,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>655495</v>
+        <v>655622</v>
       </c>
       <c r="R187" t="n">
-        <v>7331070</v>
+        <v>7331046</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21398,7 +21402,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21408,7 +21412,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21439,7 +21443,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135362063</v>
+        <v>135362062</v>
       </c>
       <c r="B188" t="n">
         <v>79373</v>
@@ -21474,10 +21478,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>655445</v>
+        <v>655495</v>
       </c>
       <c r="R188" t="n">
-        <v>7331056</v>
+        <v>7331070</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21509,7 +21513,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -21519,7 +21523,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21550,7 +21554,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135363825</v>
+        <v>135362063</v>
       </c>
       <c r="B189" t="n">
         <v>79373</v>
@@ -21585,13 +21589,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>655765</v>
+        <v>655445</v>
       </c>
       <c r="R189" t="n">
-        <v>7330816</v>
+        <v>7331056</v>
       </c>
       <c r="S189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21620,7 +21624,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21630,7 +21634,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21645,12 +21649,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -21661,32 +21665,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135359836</v>
+        <v>135363825</v>
       </c>
       <c r="B190" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21696,13 +21700,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>655835</v>
+        <v>655765</v>
       </c>
       <c r="R190" t="n">
-        <v>7330823</v>
+        <v>7330816</v>
       </c>
       <c r="S190" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21731,7 +21735,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21741,7 +21745,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21756,12 +21760,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -21772,10 +21776,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135357739</v>
+        <v>135359836</v>
       </c>
       <c r="B191" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21783,40 +21787,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>655599</v>
+        <v>655835</v>
       </c>
       <c r="R191" t="n">
-        <v>7330842</v>
+        <v>7330823</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21845,7 +21846,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21855,7 +21856,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21864,19 +21865,18 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -21887,7 +21887,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135359830</v>
+        <v>135357739</v>
       </c>
       <c r="B192" t="n">
         <v>83358</v>
@@ -21916,16 +21916,19 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>655798</v>
+        <v>655599</v>
       </c>
       <c r="R192" t="n">
-        <v>7330738</v>
+        <v>7330842</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -21957,7 +21960,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21967,7 +21970,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21976,18 +21979,19 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -21998,7 +22002,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135359831</v>
+        <v>135359830</v>
       </c>
       <c r="B193" t="n">
         <v>83358</v>
@@ -22033,10 +22037,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>655805</v>
+        <v>655798</v>
       </c>
       <c r="R193" t="n">
-        <v>7330737</v>
+        <v>7330738</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22109,48 +22113,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135357746</v>
+        <v>135359831</v>
       </c>
       <c r="B194" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>655726</v>
+        <v>655805</v>
       </c>
       <c r="R194" t="n">
-        <v>7330840</v>
+        <v>7330737</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22179,7 +22183,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22189,7 +22193,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22204,12 +22208,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -22220,7 +22224,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135357748</v>
+        <v>135357746</v>
       </c>
       <c r="B195" t="n">
         <v>80493</v>
@@ -22255,13 +22259,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>655719</v>
+        <v>655726</v>
       </c>
       <c r="R195" t="n">
-        <v>7330846</v>
+        <v>7330840</v>
       </c>
       <c r="S195" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22290,7 +22294,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22300,7 +22304,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22331,7 +22335,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135359842</v>
+        <v>135357748</v>
       </c>
       <c r="B196" t="n">
         <v>80493</v>
@@ -22362,17 +22366,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>655720</v>
+        <v>655719</v>
       </c>
       <c r="R196" t="n">
-        <v>7330841</v>
+        <v>7330846</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22401,7 +22405,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22411,7 +22415,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22426,12 +22430,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -22442,7 +22446,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135359846</v>
+        <v>135359842</v>
       </c>
       <c r="B197" t="n">
         <v>80493</v>
@@ -22477,10 +22481,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>655723</v>
+        <v>655720</v>
       </c>
       <c r="R197" t="n">
-        <v>7330846</v>
+        <v>7330841</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22512,7 +22516,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22522,7 +22526,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22553,10 +22557,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135357747</v>
+        <v>135359846</v>
       </c>
       <c r="B198" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22564,34 +22568,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>655731</v>
+        <v>655723</v>
       </c>
       <c r="R198" t="n">
-        <v>7330836</v>
+        <v>7330846</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22623,7 +22627,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22633,7 +22637,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22648,12 +22652,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -22664,7 +22668,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135359841</v>
+        <v>135357747</v>
       </c>
       <c r="B199" t="n">
         <v>80499</v>
@@ -22695,17 +22699,17 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>655722</v>
+        <v>655731</v>
       </c>
       <c r="R199" t="n">
-        <v>7330844</v>
+        <v>7330836</v>
       </c>
       <c r="S199" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22734,7 +22738,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22744,7 +22748,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22759,12 +22763,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -22775,7 +22779,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135359845</v>
+        <v>135359841</v>
       </c>
       <c r="B200" t="n">
         <v>80499</v>
@@ -22810,13 +22814,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>655723</v>
+        <v>655722</v>
       </c>
       <c r="R200" t="n">
-        <v>7330845</v>
+        <v>7330844</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22845,7 +22849,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22855,7 +22859,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22886,10 +22890,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135359843</v>
+        <v>135359845</v>
       </c>
       <c r="B201" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22897,21 +22901,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22924,7 +22928,7 @@
         <v>655723</v>
       </c>
       <c r="R201" t="n">
-        <v>7330841</v>
+        <v>7330845</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -22956,7 +22960,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22966,7 +22970,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22997,7 +23001,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135359847</v>
+        <v>135359843</v>
       </c>
       <c r="B202" t="n">
         <v>80500</v>
@@ -23035,7 +23039,7 @@
         <v>655723</v>
       </c>
       <c r="R202" t="n">
-        <v>7330846</v>
+        <v>7330841</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23067,7 +23071,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23077,7 +23081,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23108,53 +23112,48 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135313442</v>
+        <v>135359847</v>
       </c>
       <c r="B203" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>655548</v>
+        <v>655723</v>
       </c>
       <c r="R203" t="n">
-        <v>7330875</v>
+        <v>7330846</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -23178,12 +23177,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23198,19 +23207,23 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY203" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135357407</v>
+        <v>135313442</v>
       </c>
       <c r="B204" t="n">
         <v>57975</v>
@@ -23239,19 +23252,24 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>655446</v>
+        <v>655548</v>
       </c>
       <c r="R204" t="n">
-        <v>7330950</v>
+        <v>7330875</v>
       </c>
       <c r="S204" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23275,27 +23293,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23310,23 +23313,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135357742</v>
+        <v>135357407</v>
       </c>
       <c r="B205" t="n">
         <v>57975</v>
@@ -23357,17 +23356,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>655598</v>
+        <v>655446</v>
       </c>
       <c r="R205" t="n">
-        <v>7330813</v>
+        <v>7330950</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23396,7 +23395,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23406,12 +23405,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Ringhack, äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23426,12 +23425,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -23442,7 +23441,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135357749</v>
+        <v>135357742</v>
       </c>
       <c r="B206" t="n">
         <v>57975</v>
@@ -23477,10 +23476,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>655721</v>
+        <v>655598</v>
       </c>
       <c r="R206" t="n">
-        <v>7330844</v>
+        <v>7330813</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23512,7 +23511,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23522,7 +23521,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -23558,7 +23557,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135357861</v>
+        <v>135357749</v>
       </c>
       <c r="B207" t="n">
         <v>57975</v>
@@ -23587,24 +23586,19 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>655427</v>
+        <v>655721</v>
       </c>
       <c r="R207" t="n">
-        <v>7330867</v>
+        <v>7330844</v>
       </c>
       <c r="S207" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23633,7 +23627,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23643,12 +23637,12 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23663,19 +23657,23 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>135357863</v>
+        <v>135357861</v>
       </c>
       <c r="B208" t="n">
         <v>57975</v>
@@ -23715,10 +23713,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>655432</v>
+        <v>655427</v>
       </c>
       <c r="R208" t="n">
-        <v>7330859</v>
+        <v>7330867</v>
       </c>
       <c r="S208" t="n">
         <v>3</v>
@@ -23750,7 +23748,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23760,7 +23758,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -23792,7 +23790,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135357864</v>
+        <v>135357863</v>
       </c>
       <c r="B209" t="n">
         <v>57975</v>
@@ -23832,10 +23830,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>655443</v>
+        <v>655432</v>
       </c>
       <c r="R209" t="n">
-        <v>7330856</v>
+        <v>7330859</v>
       </c>
       <c r="S209" t="n">
         <v>3</v>
@@ -23867,7 +23865,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23877,7 +23875,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -23909,7 +23907,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135357865</v>
+        <v>135357864</v>
       </c>
       <c r="B210" t="n">
         <v>57975</v>
@@ -23949,10 +23947,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>655447</v>
+        <v>655443</v>
       </c>
       <c r="R210" t="n">
-        <v>7330838</v>
+        <v>7330856</v>
       </c>
       <c r="S210" t="n">
         <v>3</v>
@@ -23984,7 +23982,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23994,7 +23992,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -24026,7 +24024,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135357869</v>
+        <v>135357865</v>
       </c>
       <c r="B211" t="n">
         <v>57975</v>
@@ -24057,7 +24055,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -24066,10 +24064,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>655554</v>
+        <v>655447</v>
       </c>
       <c r="R211" t="n">
-        <v>7330873</v>
+        <v>7330838</v>
       </c>
       <c r="S211" t="n">
         <v>3</v>
@@ -24101,7 +24099,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24111,12 +24109,12 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24143,7 +24141,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135357879</v>
+        <v>135357869</v>
       </c>
       <c r="B212" t="n">
         <v>57975</v>
@@ -24174,7 +24172,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -24183,10 +24181,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>655572</v>
+        <v>655554</v>
       </c>
       <c r="R212" t="n">
-        <v>7330861</v>
+        <v>7330873</v>
       </c>
       <c r="S212" t="n">
         <v>3</v>
@@ -24218,7 +24216,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24228,12 +24226,12 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24260,7 +24258,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135357885</v>
+        <v>135357879</v>
       </c>
       <c r="B213" t="n">
         <v>57975</v>
@@ -24291,7 +24289,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -24300,10 +24298,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>655629</v>
+        <v>655572</v>
       </c>
       <c r="R213" t="n">
-        <v>7330853</v>
+        <v>7330861</v>
       </c>
       <c r="S213" t="n">
         <v>3</v>
@@ -24335,7 +24333,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24345,12 +24343,12 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24377,7 +24375,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135357894</v>
+        <v>135357885</v>
       </c>
       <c r="B214" t="n">
         <v>57975</v>
@@ -24417,10 +24415,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>655779</v>
+        <v>655629</v>
       </c>
       <c r="R214" t="n">
-        <v>7330760</v>
+        <v>7330853</v>
       </c>
       <c r="S214" t="n">
         <v>3</v>
@@ -24452,7 +24450,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24462,12 +24460,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Medelhög livsmiljövärde</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24494,7 +24492,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135357902</v>
+        <v>135357894</v>
       </c>
       <c r="B215" t="n">
         <v>57975</v>
@@ -24525,7 +24523,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24534,10 +24532,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>655610</v>
+        <v>655779</v>
       </c>
       <c r="R215" t="n">
-        <v>7330878</v>
+        <v>7330760</v>
       </c>
       <c r="S215" t="n">
         <v>3</v>
@@ -24569,7 +24567,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24579,12 +24577,12 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Medelhög livsmiljövärde</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24611,7 +24609,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135357906</v>
+        <v>135357902</v>
       </c>
       <c r="B216" t="n">
         <v>57975</v>
@@ -24651,10 +24649,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>655510</v>
+        <v>655610</v>
       </c>
       <c r="R216" t="n">
-        <v>7330908</v>
+        <v>7330878</v>
       </c>
       <c r="S216" t="n">
         <v>3</v>
@@ -24686,7 +24684,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -24696,7 +24694,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -24728,7 +24726,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135359803</v>
+        <v>135357906</v>
       </c>
       <c r="B217" t="n">
         <v>57975</v>
@@ -24757,19 +24755,24 @@
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>655451</v>
+        <v>655510</v>
       </c>
       <c r="R217" t="n">
-        <v>7330842</v>
+        <v>7330908</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24798,7 +24801,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24808,12 +24811,12 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24828,23 +24831,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY217" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135362057</v>
+        <v>135359803</v>
       </c>
       <c r="B218" t="n">
         <v>57975</v>
@@ -24873,24 +24872,16 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>655531</v>
+        <v>655451</v>
       </c>
       <c r="R218" t="n">
-        <v>7331104</v>
+        <v>7330842</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24922,7 +24913,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24932,7 +24923,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24947,12 +24943,12 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -24963,7 +24959,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135362059</v>
+        <v>135362057</v>
       </c>
       <c r="B219" t="n">
         <v>57975</v>
@@ -25006,10 +25002,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>655629</v>
+        <v>655531</v>
       </c>
       <c r="R219" t="n">
-        <v>7331036</v>
+        <v>7331104</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -25041,7 +25037,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25051,7 +25047,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25082,7 +25078,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135362064</v>
+        <v>135362059</v>
       </c>
       <c r="B220" t="n">
         <v>57975</v>
@@ -25125,13 +25121,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>655445</v>
+        <v>655629</v>
       </c>
       <c r="R220" t="n">
-        <v>7331056</v>
+        <v>7331036</v>
       </c>
       <c r="S220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -25160,7 +25156,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25170,7 +25166,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25201,64 +25197,56 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135357903</v>
+        <v>135362064</v>
       </c>
       <c r="B221" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>655565</v>
+        <v>655445</v>
       </c>
       <c r="R221" t="n">
-        <v>7330914</v>
+        <v>7331056</v>
       </c>
       <c r="S221" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25287,7 +25275,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25297,7 +25285,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25312,22 +25300,26 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135359824</v>
+        <v>135357903</v>
       </c>
       <c r="B222" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25335,37 +25327,53 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>655631</v>
+        <v>655565</v>
       </c>
       <c r="R222" t="n">
-        <v>7330798</v>
+        <v>7330914</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25394,7 +25402,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25404,7 +25412,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25419,48 +25427,44 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135359839</v>
+        <v>135359824</v>
       </c>
       <c r="B223" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25470,10 +25474,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>655777</v>
+        <v>655631</v>
       </c>
       <c r="R223" t="n">
-        <v>7330820</v>
+        <v>7330798</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -25505,7 +25509,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25515,7 +25519,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25546,32 +25550,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135363827</v>
+        <v>135359839</v>
       </c>
       <c r="B224" t="n">
-        <v>99197</v>
+        <v>58136</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>219811</v>
+        <v>103021</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25581,7 +25585,7 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>655525</v>
+        <v>655777</v>
       </c>
       <c r="R224" t="n">
         <v>7330820</v>
@@ -25616,7 +25620,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25626,7 +25630,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25641,12 +25645,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25657,10 +25661,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135357398</v>
+        <v>135363827</v>
       </c>
       <c r="B225" t="n">
-        <v>99099</v>
+        <v>99197</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25668,21 +25672,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25692,10 +25696,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>655579</v>
+        <v>655525</v>
       </c>
       <c r="R225" t="n">
-        <v>7330863</v>
+        <v>7330820</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -25727,7 +25731,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25737,7 +25741,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25752,12 +25756,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -25768,7 +25772,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135357400</v>
+        <v>135357398</v>
       </c>
       <c r="B226" t="n">
         <v>99099</v>
@@ -25803,13 +25807,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R226" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25838,7 +25842,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25848,7 +25852,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25879,7 +25883,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135359822</v>
+        <v>135357400</v>
       </c>
       <c r="B227" t="n">
         <v>99099</v>
@@ -25914,13 +25918,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>655610</v>
+        <v>655621</v>
       </c>
       <c r="R227" t="n">
-        <v>7330795</v>
+        <v>7330834</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25949,7 +25953,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25959,7 +25963,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25974,12 +25978,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -25990,10 +25994,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135357395</v>
+        <v>135359822</v>
       </c>
       <c r="B228" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26001,21 +26005,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -26025,13 +26029,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>655546</v>
+        <v>655610</v>
       </c>
       <c r="R228" t="n">
-        <v>7330858</v>
+        <v>7330795</v>
       </c>
       <c r="S228" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26060,7 +26064,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26070,7 +26074,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26085,12 +26089,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26101,7 +26105,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135357397</v>
+        <v>135357395</v>
       </c>
       <c r="B229" t="n">
         <v>99217</v>
@@ -26136,13 +26140,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>655579</v>
+        <v>655546</v>
       </c>
       <c r="R229" t="n">
-        <v>7330863</v>
+        <v>7330858</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26171,7 +26175,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26181,7 +26185,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26212,7 +26216,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135357399</v>
+        <v>135357397</v>
       </c>
       <c r="B230" t="n">
         <v>99217</v>
@@ -26247,13 +26251,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R230" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S230" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26282,7 +26286,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -26292,7 +26296,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26323,7 +26327,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135357401</v>
+        <v>135357399</v>
       </c>
       <c r="B231" t="n">
         <v>99217</v>
@@ -26358,13 +26362,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>655806</v>
+        <v>655621</v>
       </c>
       <c r="R231" t="n">
-        <v>7330742</v>
+        <v>7330834</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26393,7 +26397,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26403,7 +26407,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26434,7 +26438,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135357402</v>
+        <v>135357401</v>
       </c>
       <c r="B232" t="n">
         <v>99217</v>
@@ -26469,10 +26473,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>655842</v>
+        <v>655806</v>
       </c>
       <c r="R232" t="n">
-        <v>7330740</v>
+        <v>7330742</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -26504,7 +26508,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26514,7 +26518,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26545,7 +26549,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135357403</v>
+        <v>135357402</v>
       </c>
       <c r="B233" t="n">
         <v>99217</v>
@@ -26580,10 +26584,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>655735</v>
+        <v>655842</v>
       </c>
       <c r="R233" t="n">
-        <v>7330853</v>
+        <v>7330740</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -26615,7 +26619,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26625,7 +26629,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26656,7 +26660,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135357405</v>
+        <v>135357403</v>
       </c>
       <c r="B234" t="n">
         <v>99217</v>
@@ -26691,13 +26695,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>655649</v>
+        <v>655735</v>
       </c>
       <c r="R234" t="n">
-        <v>7330872</v>
+        <v>7330853</v>
       </c>
       <c r="S234" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26726,7 +26730,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26736,7 +26740,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26767,7 +26771,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135357406</v>
+        <v>135357405</v>
       </c>
       <c r="B235" t="n">
         <v>99217</v>
@@ -26802,13 +26806,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>655448</v>
+        <v>655649</v>
       </c>
       <c r="R235" t="n">
-        <v>7330951</v>
+        <v>7330872</v>
       </c>
       <c r="S235" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26837,7 +26841,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26847,7 +26851,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26878,7 +26882,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135359811</v>
+        <v>135357406</v>
       </c>
       <c r="B236" t="n">
         <v>99217</v>
@@ -26913,13 +26917,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>655554</v>
+        <v>655448</v>
       </c>
       <c r="R236" t="n">
-        <v>7330834</v>
+        <v>7330951</v>
       </c>
       <c r="S236" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26948,7 +26952,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26958,12 +26962,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26978,12 +26977,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26994,7 +26993,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135359812</v>
+        <v>135359811</v>
       </c>
       <c r="B237" t="n">
         <v>99217</v>
@@ -27029,13 +27028,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>655568</v>
+        <v>655554</v>
       </c>
       <c r="R237" t="n">
-        <v>7330829</v>
+        <v>7330834</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -27064,7 +27063,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27074,12 +27073,12 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>4 exemplar</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27110,7 +27109,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135359813</v>
+        <v>135359812</v>
       </c>
       <c r="B238" t="n">
         <v>99217</v>
@@ -27145,13 +27144,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>655571</v>
+        <v>655568</v>
       </c>
       <c r="R238" t="n">
-        <v>7330837</v>
+        <v>7330829</v>
       </c>
       <c r="S238" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27180,7 +27179,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27190,12 +27189,12 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>4 exemplar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27226,7 +27225,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135359821</v>
+        <v>135359813</v>
       </c>
       <c r="B239" t="n">
         <v>99217</v>
@@ -27261,13 +27260,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>655613</v>
+        <v>655571</v>
       </c>
       <c r="R239" t="n">
-        <v>7330794</v>
+        <v>7330837</v>
       </c>
       <c r="S239" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27296,7 +27295,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27306,7 +27305,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
@@ -27342,7 +27341,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135359838</v>
+        <v>135359821</v>
       </c>
       <c r="B240" t="n">
         <v>99217</v>
@@ -27377,10 +27376,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>655778</v>
+        <v>655613</v>
       </c>
       <c r="R240" t="n">
-        <v>7330823</v>
+        <v>7330794</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -27412,7 +27411,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27422,7 +27421,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -27458,7 +27457,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135359851</v>
+        <v>135359838</v>
       </c>
       <c r="B241" t="n">
         <v>99217</v>
@@ -27493,13 +27492,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>655429</v>
+        <v>655778</v>
       </c>
       <c r="R241" t="n">
-        <v>7330949</v>
+        <v>7330823</v>
       </c>
       <c r="S241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27528,7 +27527,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27538,7 +27537,12 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27569,7 +27573,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135363823</v>
+        <v>135359851</v>
       </c>
       <c r="B242" t="n">
         <v>99217</v>
@@ -27604,13 +27608,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>655537</v>
+        <v>655429</v>
       </c>
       <c r="R242" t="n">
-        <v>7330838</v>
+        <v>7330949</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27639,7 +27643,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27649,7 +27653,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27664,12 +27668,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27680,32 +27684,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135357608</v>
+        <v>135363823</v>
       </c>
       <c r="B243" t="n">
-        <v>79452</v>
+        <v>99217</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>864</v>
+        <v>221952</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27715,10 +27719,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>655448</v>
+        <v>655537</v>
       </c>
       <c r="R243" t="n">
-        <v>7331407</v>
+        <v>7330838</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -27750,7 +27754,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27760,12 +27764,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27780,12 +27779,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -27796,7 +27795,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135362050</v>
+        <v>135357608</v>
       </c>
       <c r="B244" t="n">
         <v>79452</v>
@@ -27831,10 +27830,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>655450</v>
+        <v>655448</v>
       </c>
       <c r="R244" t="n">
-        <v>7331353</v>
+        <v>7331407</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -27866,7 +27865,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27876,7 +27875,12 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27891,12 +27895,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27907,7 +27911,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135362051</v>
+        <v>135362050</v>
       </c>
       <c r="B245" t="n">
         <v>79452</v>
@@ -27942,13 +27946,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>655435</v>
+        <v>655450</v>
       </c>
       <c r="R245" t="n">
-        <v>7331358</v>
+        <v>7331353</v>
       </c>
       <c r="S245" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27977,7 +27981,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27987,7 +27991,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27996,7 +28000,6 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -28019,32 +28022,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135357607</v>
+        <v>135362051</v>
       </c>
       <c r="B246" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28054,13 +28057,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>655444</v>
+        <v>655435</v>
       </c>
       <c r="R246" t="n">
-        <v>7331409</v>
+        <v>7331358</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28089,7 +28092,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28099,12 +28102,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28113,18 +28111,19 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -28135,7 +28134,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135357609</v>
+        <v>135357607</v>
       </c>
       <c r="B247" t="n">
         <v>79373</v>
@@ -28170,13 +28169,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>655447</v>
+        <v>655444</v>
       </c>
       <c r="R247" t="n">
-        <v>7331408</v>
+        <v>7331409</v>
       </c>
       <c r="S247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28205,7 +28204,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28215,7 +28214,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28246,7 +28250,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135357610</v>
+        <v>135357609</v>
       </c>
       <c r="B248" t="n">
         <v>79373</v>
@@ -28281,13 +28285,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>655445</v>
+        <v>655447</v>
       </c>
       <c r="R248" t="n">
-        <v>7331409</v>
+        <v>7331408</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28357,7 +28361,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135357613</v>
+        <v>135357610</v>
       </c>
       <c r="B249" t="n">
         <v>79373</v>
@@ -28392,13 +28396,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>655422</v>
+        <v>655445</v>
       </c>
       <c r="R249" t="n">
-        <v>7331225</v>
+        <v>7331409</v>
       </c>
       <c r="S249" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28427,7 +28431,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28437,7 +28441,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28468,7 +28472,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135357614</v>
+        <v>135357613</v>
       </c>
       <c r="B250" t="n">
         <v>79373</v>
@@ -28506,10 +28510,10 @@
         <v>655422</v>
       </c>
       <c r="R250" t="n">
-        <v>7331227</v>
+        <v>7331225</v>
       </c>
       <c r="S250" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28538,7 +28542,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28548,7 +28552,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28579,7 +28583,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135357615</v>
+        <v>135357614</v>
       </c>
       <c r="B251" t="n">
         <v>79373</v>
@@ -28614,13 +28618,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>655423</v>
+        <v>655422</v>
       </c>
       <c r="R251" t="n">
-        <v>7331217</v>
+        <v>7331227</v>
       </c>
       <c r="S251" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28649,7 +28653,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28659,7 +28663,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28690,7 +28694,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135362056</v>
+        <v>135357615</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28725,13 +28729,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>655425</v>
+        <v>655423</v>
       </c>
       <c r="R252" t="n">
-        <v>7331260</v>
+        <v>7331217</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28760,7 +28764,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28770,7 +28774,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28785,12 +28789,12 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -28801,56 +28805,48 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135362049</v>
+        <v>135362056</v>
       </c>
       <c r="B253" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>655450</v>
+        <v>655425</v>
       </c>
       <c r="R253" t="n">
-        <v>7331381</v>
+        <v>7331260</v>
       </c>
       <c r="S253" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28879,7 +28875,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28889,7 +28885,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28913,6 +28909,125 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>135362049</v>
+      </c>
+      <c r="B254" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>655450</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7331381</v>
+      </c>
+      <c r="S254" t="n">
+        <v>5</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -6864,7 +6864,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -6864,7 +6864,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -25761,7 +25761,7 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -27784,7 +27784,7 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY254"/>
+  <dimension ref="A1:AY255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12562,48 +12562,53 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135359099</v>
+        <v>135519109</v>
       </c>
       <c r="B108" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655346</v>
+        <v>655335</v>
       </c>
       <c r="R108" t="n">
-        <v>7331111</v>
+        <v>7331100</v>
       </c>
       <c r="S108" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12632,7 +12637,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12642,12 +12647,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12662,26 +12662,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Maja Josefsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135363819</v>
+        <v>135359099</v>
       </c>
       <c r="B109" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12689,42 +12685,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>655323</v>
+        <v>655346</v>
       </c>
       <c r="R109" t="n">
-        <v>7330913</v>
+        <v>7331111</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12753,7 +12744,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12763,7 +12754,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Satt på grov tallgren, cirka 2,5 m upp från mark, lämnade fjädrar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12774,31 +12770,16 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Maja Josefsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12809,10 +12790,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356795</v>
+        <v>135363819</v>
       </c>
       <c r="B110" t="n">
-        <v>5201</v>
+        <v>5181</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12820,34 +12801,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>655319</v>
+        <v>655323</v>
       </c>
       <c r="R110" t="n">
-        <v>7330993</v>
+        <v>7330913</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12879,7 +12865,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12889,7 +12875,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12900,16 +12886,31 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12920,7 +12921,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135363820</v>
+        <v>135356795</v>
       </c>
       <c r="B111" t="n">
         <v>5201</v>
@@ -12949,21 +12950,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655315</v>
+        <v>655319</v>
       </c>
       <c r="R111" t="n">
-        <v>7330919</v>
+        <v>7330993</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12995,7 +12991,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13005,7 +13001,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13016,31 +13012,16 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13051,27 +13032,27 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135359792</v>
+        <v>135363820</v>
       </c>
       <c r="B112" t="n">
-        <v>56706</v>
+        <v>5201</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>206046</v>
+        <v>105930</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -13080,16 +13061,21 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>655330</v>
+        <v>655315</v>
       </c>
       <c r="R112" t="n">
-        <v>7330904</v>
+        <v>7330919</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13121,7 +13107,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13131,7 +13117,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13142,16 +13128,31 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13162,10 +13163,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135357600</v>
+        <v>135359792</v>
       </c>
       <c r="B113" t="n">
-        <v>79452</v>
+        <v>56706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13173,21 +13174,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>864</v>
+        <v>206046</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13197,10 +13198,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>655383</v>
+        <v>655330</v>
       </c>
       <c r="R113" t="n">
-        <v>7331249</v>
+        <v>7330904</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13232,7 +13233,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13242,7 +13243,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13257,12 +13258,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13273,32 +13274,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135357596</v>
+        <v>135357600</v>
       </c>
       <c r="B114" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13308,10 +13309,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655350</v>
+        <v>655383</v>
       </c>
       <c r="R114" t="n">
-        <v>7331177</v>
+        <v>7331249</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13343,7 +13344,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13353,7 +13354,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13384,7 +13385,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135357598</v>
+        <v>135357596</v>
       </c>
       <c r="B115" t="n">
         <v>79373</v>
@@ -13419,10 +13420,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>655386</v>
+        <v>655350</v>
       </c>
       <c r="R115" t="n">
-        <v>7331245</v>
+        <v>7331177</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13454,7 +13455,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13464,7 +13465,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13495,7 +13496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135357601</v>
+        <v>135357598</v>
       </c>
       <c r="B116" t="n">
         <v>79373</v>
@@ -13530,10 +13531,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>655380</v>
+        <v>655386</v>
       </c>
       <c r="R116" t="n">
-        <v>7331257</v>
+        <v>7331245</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13565,7 +13566,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13575,7 +13576,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13606,7 +13607,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135357604</v>
+        <v>135357601</v>
       </c>
       <c r="B117" t="n">
         <v>79373</v>
@@ -13641,10 +13642,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>655385</v>
+        <v>655380</v>
       </c>
       <c r="R117" t="n">
-        <v>7331284</v>
+        <v>7331257</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13676,7 +13677,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13686,7 +13687,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13717,7 +13718,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135357605</v>
+        <v>135357604</v>
       </c>
       <c r="B118" t="n">
         <v>79373</v>
@@ -13752,10 +13753,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>655401</v>
+        <v>655385</v>
       </c>
       <c r="R118" t="n">
-        <v>7331323</v>
+        <v>7331284</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13787,7 +13788,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13797,7 +13798,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13828,7 +13829,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135357612</v>
+        <v>135357605</v>
       </c>
       <c r="B119" t="n">
         <v>79373</v>
@@ -13863,10 +13864,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>655419</v>
+        <v>655401</v>
       </c>
       <c r="R119" t="n">
-        <v>7331234</v>
+        <v>7331323</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13898,7 +13899,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13908,7 +13909,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13939,7 +13940,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135357616</v>
+        <v>135357612</v>
       </c>
       <c r="B120" t="n">
         <v>79373</v>
@@ -13974,10 +13975,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>655412</v>
+        <v>655419</v>
       </c>
       <c r="R120" t="n">
-        <v>7331202</v>
+        <v>7331234</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14009,7 +14010,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14019,7 +14020,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14050,7 +14051,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135358261</v>
+        <v>135357616</v>
       </c>
       <c r="B121" t="n">
         <v>79373</v>
@@ -14085,13 +14086,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>655366</v>
+        <v>655412</v>
       </c>
       <c r="R121" t="n">
-        <v>7331190</v>
+        <v>7331202</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14118,9 +14119,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14135,12 +14146,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14151,7 +14162,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135362048</v>
+        <v>135358261</v>
       </c>
       <c r="B122" t="n">
         <v>79373</v>
@@ -14186,13 +14197,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>655385</v>
+        <v>655366</v>
       </c>
       <c r="R122" t="n">
-        <v>7331203</v>
+        <v>7331190</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14219,19 +14230,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14246,12 +14247,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14262,7 +14263,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135362055</v>
+        <v>135362048</v>
       </c>
       <c r="B123" t="n">
         <v>79373</v>
@@ -14297,10 +14298,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>655412</v>
+        <v>655385</v>
       </c>
       <c r="R123" t="n">
-        <v>7331313</v>
+        <v>7331203</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14332,7 +14333,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14342,7 +14343,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14373,32 +14374,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135362052</v>
+        <v>135362055</v>
       </c>
       <c r="B124" t="n">
-        <v>80500</v>
+        <v>79373</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14411,7 +14412,7 @@
         <v>655412</v>
       </c>
       <c r="R124" t="n">
-        <v>7331334</v>
+        <v>7331313</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14443,7 +14444,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14453,7 +14454,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14484,52 +14485,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135362054</v>
+        <v>135362052</v>
       </c>
       <c r="B125" t="n">
-        <v>57896</v>
+        <v>80500</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100001</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>655399</v>
+        <v>655412</v>
       </c>
       <c r="R125" t="n">
-        <v>7331367</v>
+        <v>7331334</v>
       </c>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14558,7 +14555,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14568,7 +14565,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14599,10 +14596,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135357743</v>
+        <v>135362054</v>
       </c>
       <c r="B126" t="n">
-        <v>97435</v>
+        <v>57896</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14610,37 +14607,41 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>53</v>
+        <v>100001</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>655691</v>
+        <v>655399</v>
       </c>
       <c r="R126" t="n">
-        <v>7330830</v>
+        <v>7331367</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14669,7 +14670,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14679,12 +14680,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Elin götmark</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14699,12 +14695,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14715,10 +14711,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135357753</v>
+        <v>135357743</v>
       </c>
       <c r="B127" t="n">
-        <v>91924</v>
+        <v>97435</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14726,37 +14722,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>655469</v>
+        <v>655691</v>
       </c>
       <c r="R127" t="n">
-        <v>7330945</v>
+        <v>7330830</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14788,7 +14781,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14798,7 +14791,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Elin götmark</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14807,7 +14805,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14830,7 +14827,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135359820</v>
+        <v>135357753</v>
       </c>
       <c r="B128" t="n">
         <v>91924</v>
@@ -14859,16 +14856,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>655580</v>
+        <v>655469</v>
       </c>
       <c r="R128" t="n">
-        <v>7330839</v>
+        <v>7330945</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14926,12 +14926,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14942,10 +14942,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135357874</v>
+        <v>135359820</v>
       </c>
       <c r="B129" t="n">
-        <v>92245</v>
+        <v>91924</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,21 +14953,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14977,13 +14977,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>655554</v>
+        <v>655580</v>
       </c>
       <c r="R129" t="n">
-        <v>7330893</v>
+        <v>7330839</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15031,69 +15031,71 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135357745</v>
+        <v>135357874</v>
       </c>
       <c r="B130" t="n">
-        <v>92546</v>
+        <v>92245</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>655712</v>
+        <v>655554</v>
       </c>
       <c r="R130" t="n">
-        <v>7330827</v>
+        <v>7330893</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15122,7 +15124,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15132,7 +15134,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15141,71 +15143,69 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135313461</v>
+        <v>135357745</v>
       </c>
       <c r="B131" t="n">
-        <v>79452</v>
+        <v>92546</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>655548</v>
+        <v>655712</v>
       </c>
       <c r="R131" t="n">
-        <v>7330875</v>
+        <v>7330827</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15229,12 +15229,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15243,45 +15253,30 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Katharina Radloff, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135358264</v>
+        <v>135313461</v>
       </c>
       <c r="B132" t="n">
         <v>79452</v>
@@ -15312,17 +15307,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>655581</v>
+        <v>655548</v>
       </c>
       <c r="R132" t="n">
-        <v>7330768</v>
+        <v>7330875</v>
       </c>
       <c r="S132" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15346,12 +15341,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15362,27 +15357,43 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135359833</v>
+        <v>135358264</v>
       </c>
       <c r="B133" t="n">
         <v>79452</v>
@@ -15417,13 +15428,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>655912</v>
+        <v>655581</v>
       </c>
       <c r="R133" t="n">
-        <v>7330763</v>
+        <v>7330768</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15450,24 +15461,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15482,12 +15478,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15498,7 +15494,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135362060</v>
+        <v>135359833</v>
       </c>
       <c r="B134" t="n">
         <v>79452</v>
@@ -15533,13 +15529,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>655623</v>
+        <v>655912</v>
       </c>
       <c r="R134" t="n">
-        <v>7331034</v>
+        <v>7330763</v>
       </c>
       <c r="S134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15568,7 +15564,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15578,7 +15574,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15593,12 +15594,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15609,7 +15610,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135362061</v>
+        <v>135362060</v>
       </c>
       <c r="B135" t="n">
         <v>79452</v>
@@ -15644,13 +15645,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>655532</v>
+        <v>655623</v>
       </c>
       <c r="R135" t="n">
-        <v>7331066</v>
+        <v>7331034</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15679,7 +15680,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15689,7 +15690,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15720,32 +15721,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135357881</v>
+        <v>135362061</v>
       </c>
       <c r="B136" t="n">
-        <v>92689</v>
+        <v>79452</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>898</v>
+        <v>864</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15755,13 +15756,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>655582</v>
+        <v>655532</v>
       </c>
       <c r="R136" t="n">
-        <v>7330866</v>
+        <v>7331066</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15790,7 +15791,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15800,7 +15801,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15815,22 +15816,26 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135363826</v>
+        <v>135357881</v>
       </c>
       <c r="B137" t="n">
-        <v>92795</v>
+        <v>92689</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,21 +15843,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15862,13 +15867,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>655667</v>
+        <v>655582</v>
       </c>
       <c r="R137" t="n">
-        <v>7330915</v>
+        <v>7330866</v>
       </c>
       <c r="S137" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15897,7 +15902,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15907,7 +15912,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15918,86 +15923,64 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Granlåga intill kärr # Picea abies</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135357752</v>
+        <v>135363826</v>
       </c>
       <c r="B138" t="n">
-        <v>91974</v>
+        <v>92795</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>655556</v>
+        <v>655667</v>
       </c>
       <c r="R138" t="n">
-        <v>7330931</v>
+        <v>7330915</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16026,7 +16009,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16036,7 +16019,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16045,19 +16028,33 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Granlåga intill kärr # Picea abies</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Linda Nordström</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -16068,7 +16065,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135357859</v>
+        <v>135357752</v>
       </c>
       <c r="B139" t="n">
         <v>91974</v>
@@ -16097,19 +16094,22 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>655424</v>
+        <v>655556</v>
       </c>
       <c r="R139" t="n">
-        <v>7330873</v>
+        <v>7330931</v>
       </c>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16157,25 +16157,30 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Katharina Radloff, Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135357873</v>
+        <v>135357859</v>
       </c>
       <c r="B140" t="n">
         <v>91974</v>
@@ -16210,10 +16215,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>655553</v>
+        <v>655424</v>
       </c>
       <c r="R140" t="n">
-        <v>7330893</v>
+        <v>7330873</v>
       </c>
       <c r="S140" t="n">
         <v>3</v>
@@ -16245,7 +16250,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16255,7 +16260,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16282,7 +16287,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357875</v>
+        <v>135357873</v>
       </c>
       <c r="B141" t="n">
         <v>91974</v>
@@ -16317,10 +16322,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>655551</v>
+        <v>655553</v>
       </c>
       <c r="R141" t="n">
-        <v>7330892</v>
+        <v>7330893</v>
       </c>
       <c r="S141" t="n">
         <v>3</v>
@@ -16352,7 +16357,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16362,7 +16367,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16389,7 +16394,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357882</v>
+        <v>135357875</v>
       </c>
       <c r="B142" t="n">
         <v>91974</v>
@@ -16424,10 +16429,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>655583</v>
+        <v>655551</v>
       </c>
       <c r="R142" t="n">
-        <v>7330865</v>
+        <v>7330892</v>
       </c>
       <c r="S142" t="n">
         <v>3</v>
@@ -16459,7 +16464,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16469,7 +16474,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16496,7 +16501,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357898</v>
+        <v>135357882</v>
       </c>
       <c r="B143" t="n">
         <v>91974</v>
@@ -16531,10 +16536,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>655889</v>
+        <v>655583</v>
       </c>
       <c r="R143" t="n">
-        <v>7330756</v>
+        <v>7330865</v>
       </c>
       <c r="S143" t="n">
         <v>3</v>
@@ -16566,7 +16571,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16576,7 +16581,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16603,7 +16608,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135359825</v>
+        <v>135357898</v>
       </c>
       <c r="B144" t="n">
         <v>91974</v>
@@ -16638,13 +16643,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>655631</v>
+        <v>655889</v>
       </c>
       <c r="R144" t="n">
-        <v>7330798</v>
+        <v>7330756</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16673,7 +16678,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16683,7 +16688,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16698,67 +16703,60 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135357751</v>
+        <v>135359825</v>
       </c>
       <c r="B145" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>655558</v>
+        <v>655631</v>
       </c>
       <c r="R145" t="n">
-        <v>7330935</v>
+        <v>7330798</v>
       </c>
       <c r="S145" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16787,7 +16785,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16797,12 +16795,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Elin Göt</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16811,19 +16804,18 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16834,7 +16826,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135359815</v>
+        <v>135357751</v>
       </c>
       <c r="B146" t="n">
         <v>91988</v>
@@ -16863,19 +16855,22 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>655579</v>
+        <v>655558</v>
       </c>
       <c r="R146" t="n">
-        <v>7330852</v>
+        <v>7330935</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16904,7 +16899,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16914,7 +16909,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Elin Göt</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16923,18 +16923,19 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -16945,32 +16946,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135359817</v>
+        <v>135359815</v>
       </c>
       <c r="B147" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16983,10 +16984,10 @@
         <v>655579</v>
       </c>
       <c r="R147" t="n">
-        <v>7330850</v>
+        <v>7330852</v>
       </c>
       <c r="S147" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17015,7 +17016,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17025,7 +17026,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17056,7 +17057,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135359819</v>
+        <v>135359817</v>
       </c>
       <c r="B148" t="n">
         <v>83222</v>
@@ -17091,10 +17092,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>655578</v>
+        <v>655579</v>
       </c>
       <c r="R148" t="n">
-        <v>7330838</v>
+        <v>7330850</v>
       </c>
       <c r="S148" t="n">
         <v>14</v>
@@ -17126,7 +17127,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17136,7 +17137,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17167,7 +17168,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135359834</v>
+        <v>135359819</v>
       </c>
       <c r="B149" t="n">
         <v>83222</v>
@@ -17202,13 +17203,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>655911</v>
+        <v>655578</v>
       </c>
       <c r="R149" t="n">
-        <v>7330764</v>
+        <v>7330838</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17237,7 +17238,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17247,7 +17248,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17278,7 +17279,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135359835</v>
+        <v>135359834</v>
       </c>
       <c r="B150" t="n">
         <v>83222</v>
@@ -17313,13 +17314,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>655872</v>
+        <v>655911</v>
       </c>
       <c r="R150" t="n">
-        <v>7330793</v>
+        <v>7330764</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17348,7 +17349,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17358,7 +17359,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17389,7 +17390,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135359848</v>
+        <v>135359835</v>
       </c>
       <c r="B151" t="n">
         <v>83222</v>
@@ -17424,10 +17425,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>655658</v>
+        <v>655872</v>
       </c>
       <c r="R151" t="n">
-        <v>7330855</v>
+        <v>7330793</v>
       </c>
       <c r="S151" t="n">
         <v>6</v>
@@ -17459,7 +17460,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17469,7 +17470,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17500,10 +17501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357396</v>
+        <v>135359848</v>
       </c>
       <c r="B152" t="n">
-        <v>83363</v>
+        <v>83222</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17511,21 +17512,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17535,13 +17536,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>655579</v>
+        <v>655658</v>
       </c>
       <c r="R152" t="n">
-        <v>7330863</v>
+        <v>7330855</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17570,7 +17571,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17580,7 +17581,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17589,19 +17590,18 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -17612,10 +17612,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135359850</v>
+        <v>135357396</v>
       </c>
       <c r="B153" t="n">
-        <v>92167</v>
+        <v>83363</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17623,21 +17623,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1588</v>
+        <v>1467</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17647,13 +17647,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>655609</v>
+        <v>655579</v>
       </c>
       <c r="R153" t="n">
-        <v>7330902</v>
+        <v>7330863</v>
       </c>
       <c r="S153" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17701,18 +17701,19 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -17723,51 +17724,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135388328</v>
+        <v>135359850</v>
       </c>
       <c r="B154" t="n">
-        <v>92320</v>
+        <v>92167</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2063</v>
+        <v>1588</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>655426</v>
+        <v>655609</v>
       </c>
       <c r="R154" t="n">
-        <v>7330863</v>
+        <v>7330902</v>
       </c>
       <c r="S154" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17796,7 +17794,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17806,7 +17804,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17815,19 +17813,18 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -17838,10 +17835,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135313467</v>
+        <v>135388328</v>
       </c>
       <c r="B155" t="n">
-        <v>79373</v>
+        <v>92320</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17849,37 +17846,40 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>655548</v>
+        <v>655426</v>
       </c>
       <c r="R155" t="n">
-        <v>7330875</v>
+        <v>7330863</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17903,12 +17903,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17917,25 +17927,30 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357404</v>
+        <v>135313467</v>
       </c>
       <c r="B156" t="n">
         <v>79373</v>
@@ -17966,17 +17981,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>655735</v>
+        <v>655548</v>
       </c>
       <c r="R156" t="n">
-        <v>7330853</v>
+        <v>7330875</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18000,22 +18015,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18030,23 +18035,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357620</v>
+        <v>135357404</v>
       </c>
       <c r="B157" t="n">
         <v>79373</v>
@@ -18081,10 +18082,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>655434</v>
+        <v>655735</v>
       </c>
       <c r="R157" t="n">
-        <v>7331068</v>
+        <v>7330853</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -18116,7 +18117,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18126,7 +18127,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18141,12 +18142,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -18157,7 +18158,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357621</v>
+        <v>135357620</v>
       </c>
       <c r="B158" t="n">
         <v>79373</v>
@@ -18192,10 +18193,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>655422</v>
+        <v>655434</v>
       </c>
       <c r="R158" t="n">
-        <v>7331047</v>
+        <v>7331068</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -18227,7 +18228,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18237,7 +18238,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18268,7 +18269,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135357736</v>
+        <v>135357621</v>
       </c>
       <c r="B159" t="n">
         <v>79373</v>
@@ -18299,14 +18300,14 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>655499</v>
+        <v>655422</v>
       </c>
       <c r="R159" t="n">
-        <v>7330814</v>
+        <v>7331047</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -18338,7 +18339,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18348,7 +18349,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18363,12 +18364,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -18379,7 +18380,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135357737</v>
+        <v>135357736</v>
       </c>
       <c r="B160" t="n">
         <v>79373</v>
@@ -18414,13 +18415,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>655585</v>
+        <v>655499</v>
       </c>
       <c r="R160" t="n">
-        <v>7330827</v>
+        <v>7330814</v>
       </c>
       <c r="S160" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18449,7 +18450,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18459,7 +18460,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18490,7 +18491,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135357740</v>
+        <v>135357737</v>
       </c>
       <c r="B161" t="n">
         <v>79373</v>
@@ -18525,13 +18526,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>655599</v>
+        <v>655585</v>
       </c>
       <c r="R161" t="n">
-        <v>7330842</v>
+        <v>7330827</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18560,7 +18561,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18570,7 +18571,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18601,7 +18602,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135357750</v>
+        <v>135357740</v>
       </c>
       <c r="B162" t="n">
         <v>79373</v>
@@ -18636,10 +18637,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>655648</v>
+        <v>655599</v>
       </c>
       <c r="R162" t="n">
-        <v>7330944</v>
+        <v>7330842</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18671,7 +18672,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18681,7 +18682,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18712,7 +18713,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135357858</v>
+        <v>135357750</v>
       </c>
       <c r="B163" t="n">
         <v>79373</v>
@@ -18743,17 +18744,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>655422</v>
+        <v>655648</v>
       </c>
       <c r="R163" t="n">
-        <v>7330878</v>
+        <v>7330944</v>
       </c>
       <c r="S163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18782,7 +18783,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18792,7 +18793,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18807,19 +18808,23 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135357866</v>
+        <v>135357858</v>
       </c>
       <c r="B164" t="n">
         <v>79373</v>
@@ -18854,10 +18859,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>655484</v>
+        <v>655422</v>
       </c>
       <c r="R164" t="n">
-        <v>7330859</v>
+        <v>7330878</v>
       </c>
       <c r="S164" t="n">
         <v>3</v>
@@ -18889,7 +18894,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18899,12 +18904,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18931,7 +18931,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135357867</v>
+        <v>135357866</v>
       </c>
       <c r="B165" t="n">
         <v>79373</v>
@@ -18966,10 +18966,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>655503</v>
+        <v>655484</v>
       </c>
       <c r="R165" t="n">
-        <v>7330869</v>
+        <v>7330859</v>
       </c>
       <c r="S165" t="n">
         <v>3</v>
@@ -19001,7 +19001,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -19043,7 +19043,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135357872</v>
+        <v>135357867</v>
       </c>
       <c r="B166" t="n">
         <v>79373</v>
@@ -19078,10 +19078,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>655555</v>
+        <v>655503</v>
       </c>
       <c r="R166" t="n">
-        <v>7330879</v>
+        <v>7330869</v>
       </c>
       <c r="S166" t="n">
         <v>3</v>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19123,7 +19123,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19150,7 +19155,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135357878</v>
+        <v>135357872</v>
       </c>
       <c r="B167" t="n">
         <v>79373</v>
@@ -19185,10 +19190,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>655566</v>
+        <v>655555</v>
       </c>
       <c r="R167" t="n">
-        <v>7330892</v>
+        <v>7330879</v>
       </c>
       <c r="S167" t="n">
         <v>3</v>
@@ -19220,7 +19225,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19230,7 +19235,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19257,7 +19262,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135357883</v>
+        <v>135357878</v>
       </c>
       <c r="B168" t="n">
         <v>79373</v>
@@ -19292,10 +19297,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>655585</v>
+        <v>655566</v>
       </c>
       <c r="R168" t="n">
-        <v>7330843</v>
+        <v>7330892</v>
       </c>
       <c r="S168" t="n">
         <v>3</v>
@@ -19327,7 +19332,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19337,7 +19342,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19364,7 +19369,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135357896</v>
+        <v>135357883</v>
       </c>
       <c r="B169" t="n">
         <v>79373</v>
@@ -19399,10 +19404,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>655823</v>
+        <v>655585</v>
       </c>
       <c r="R169" t="n">
-        <v>7330749</v>
+        <v>7330843</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -19434,7 +19439,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19444,7 +19449,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19471,7 +19476,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>135357897</v>
+        <v>135357896</v>
       </c>
       <c r="B170" t="n">
         <v>79373</v>
@@ -19506,10 +19511,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>655886</v>
+        <v>655823</v>
       </c>
       <c r="R170" t="n">
-        <v>7330755</v>
+        <v>7330749</v>
       </c>
       <c r="S170" t="n">
         <v>3</v>
@@ -19541,7 +19546,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19551,7 +19556,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19578,7 +19583,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>135357899</v>
+        <v>135357897</v>
       </c>
       <c r="B171" t="n">
         <v>79373</v>
@@ -19613,10 +19618,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>655753</v>
+        <v>655886</v>
       </c>
       <c r="R171" t="n">
-        <v>7330807</v>
+        <v>7330755</v>
       </c>
       <c r="S171" t="n">
         <v>3</v>
@@ -19648,7 +19653,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19658,7 +19663,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19685,7 +19690,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>135357900</v>
+        <v>135357899</v>
       </c>
       <c r="B172" t="n">
         <v>79373</v>
@@ -19720,10 +19725,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>655702</v>
+        <v>655753</v>
       </c>
       <c r="R172" t="n">
-        <v>7330809</v>
+        <v>7330807</v>
       </c>
       <c r="S172" t="n">
         <v>3</v>
@@ -19755,7 +19760,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19765,7 +19770,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19792,7 +19797,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>135357901</v>
+        <v>135357900</v>
       </c>
       <c r="B173" t="n">
         <v>79373</v>
@@ -19827,10 +19832,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>655649</v>
+        <v>655702</v>
       </c>
       <c r="R173" t="n">
-        <v>7330880</v>
+        <v>7330809</v>
       </c>
       <c r="S173" t="n">
         <v>3</v>
@@ -19862,7 +19867,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19872,7 +19877,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19899,7 +19904,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>135358262</v>
+        <v>135357901</v>
       </c>
       <c r="B174" t="n">
         <v>79373</v>
@@ -19934,13 +19939,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>655425</v>
+        <v>655649</v>
       </c>
       <c r="R174" t="n">
-        <v>7331045</v>
+        <v>7330880</v>
       </c>
       <c r="S174" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19967,9 +19972,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19984,23 +19999,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>135359801</v>
+        <v>135358262</v>
       </c>
       <c r="B175" t="n">
         <v>79373</v>
@@ -20035,13 +20046,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>655441</v>
+        <v>655425</v>
       </c>
       <c r="R175" t="n">
-        <v>7330837</v>
+        <v>7331045</v>
       </c>
       <c r="S175" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20068,19 +20079,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20095,12 +20096,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -20111,7 +20112,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135359804</v>
+        <v>135359801</v>
       </c>
       <c r="B176" t="n">
         <v>79373</v>
@@ -20146,13 +20147,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>655451</v>
+        <v>655441</v>
       </c>
       <c r="R176" t="n">
-        <v>7330843</v>
+        <v>7330837</v>
       </c>
       <c r="S176" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20181,7 +20182,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20191,7 +20192,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20222,7 +20223,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>135359805</v>
+        <v>135359804</v>
       </c>
       <c r="B177" t="n">
         <v>79373</v>
@@ -20257,13 +20258,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>655464</v>
+        <v>655451</v>
       </c>
       <c r="R177" t="n">
-        <v>7330834</v>
+        <v>7330843</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20292,7 +20293,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20302,7 +20303,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20333,7 +20334,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>135359809</v>
+        <v>135359805</v>
       </c>
       <c r="B178" t="n">
         <v>79373</v>
@@ -20368,10 +20369,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>655514</v>
+        <v>655464</v>
       </c>
       <c r="R178" t="n">
-        <v>7330831</v>
+        <v>7330834</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -20403,7 +20404,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20413,7 +20414,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20444,7 +20445,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135359810</v>
+        <v>135359809</v>
       </c>
       <c r="B179" t="n">
         <v>79373</v>
@@ -20479,10 +20480,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>655548</v>
+        <v>655514</v>
       </c>
       <c r="R179" t="n">
-        <v>7330834</v>
+        <v>7330831</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20514,7 +20515,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20524,7 +20525,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20555,7 +20556,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>135359816</v>
+        <v>135359810</v>
       </c>
       <c r="B180" t="n">
         <v>79373</v>
@@ -20590,13 +20591,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>655579</v>
+        <v>655548</v>
       </c>
       <c r="R180" t="n">
-        <v>7330851</v>
+        <v>7330834</v>
       </c>
       <c r="S180" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20625,7 +20626,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20635,7 +20636,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20666,7 +20667,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>135359818</v>
+        <v>135359816</v>
       </c>
       <c r="B181" t="n">
         <v>79373</v>
@@ -20701,13 +20702,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>655591</v>
+        <v>655579</v>
       </c>
       <c r="R181" t="n">
-        <v>7330837</v>
+        <v>7330851</v>
       </c>
       <c r="S181" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20736,7 +20737,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20746,7 +20747,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20777,7 +20778,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>135359823</v>
+        <v>135359818</v>
       </c>
       <c r="B182" t="n">
         <v>79373</v>
@@ -20812,13 +20813,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>655633</v>
+        <v>655591</v>
       </c>
       <c r="R182" t="n">
-        <v>7330807</v>
+        <v>7330837</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20847,7 +20848,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20857,7 +20858,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20888,7 +20889,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>135359829</v>
+        <v>135359823</v>
       </c>
       <c r="B183" t="n">
         <v>79373</v>
@@ -20923,13 +20924,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>655798</v>
+        <v>655633</v>
       </c>
       <c r="R183" t="n">
-        <v>7330738</v>
+        <v>7330807</v>
       </c>
       <c r="S183" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20958,7 +20959,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20968,7 +20969,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20999,7 +21000,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>135359832</v>
+        <v>135359829</v>
       </c>
       <c r="B184" t="n">
         <v>79373</v>
@@ -21034,13 +21035,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>655909</v>
+        <v>655798</v>
       </c>
       <c r="R184" t="n">
-        <v>7330765</v>
+        <v>7330738</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21069,7 +21070,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21079,7 +21080,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21110,7 +21111,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>135359837</v>
+        <v>135359832</v>
       </c>
       <c r="B185" t="n">
         <v>79373</v>
@@ -21145,13 +21146,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>655782</v>
+        <v>655909</v>
       </c>
       <c r="R185" t="n">
-        <v>7330802</v>
+        <v>7330765</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21180,7 +21181,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21190,7 +21191,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21221,7 +21222,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135359849</v>
+        <v>135359837</v>
       </c>
       <c r="B186" t="n">
         <v>79373</v>
@@ -21256,10 +21257,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>655661</v>
+        <v>655782</v>
       </c>
       <c r="R186" t="n">
-        <v>7330860</v>
+        <v>7330802</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21291,7 +21292,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21301,7 +21302,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21332,7 +21333,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135362058</v>
+        <v>135359849</v>
       </c>
       <c r="B187" t="n">
         <v>79373</v>
@@ -21367,13 +21368,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>655622</v>
+        <v>655661</v>
       </c>
       <c r="R187" t="n">
-        <v>7331046</v>
+        <v>7330860</v>
       </c>
       <c r="S187" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21402,7 +21403,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21412,7 +21413,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21427,12 +21428,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -21443,7 +21444,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135362062</v>
+        <v>135362058</v>
       </c>
       <c r="B188" t="n">
         <v>79373</v>
@@ -21478,13 +21479,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>655495</v>
+        <v>655622</v>
       </c>
       <c r="R188" t="n">
-        <v>7331070</v>
+        <v>7331046</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21513,7 +21514,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -21523,7 +21524,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21554,7 +21555,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135362063</v>
+        <v>135362062</v>
       </c>
       <c r="B189" t="n">
         <v>79373</v>
@@ -21589,10 +21590,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>655445</v>
+        <v>655495</v>
       </c>
       <c r="R189" t="n">
-        <v>7331056</v>
+        <v>7331070</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21624,7 +21625,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21634,7 +21635,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21665,7 +21666,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135363825</v>
+        <v>135362063</v>
       </c>
       <c r="B190" t="n">
         <v>79373</v>
@@ -21700,13 +21701,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>655765</v>
+        <v>655445</v>
       </c>
       <c r="R190" t="n">
-        <v>7330816</v>
+        <v>7331056</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21735,7 +21736,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21745,7 +21746,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21760,12 +21761,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -21776,32 +21777,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135359836</v>
+        <v>135363825</v>
       </c>
       <c r="B191" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21811,13 +21812,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>655835</v>
+        <v>655765</v>
       </c>
       <c r="R191" t="n">
-        <v>7330823</v>
+        <v>7330816</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21846,7 +21847,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21856,7 +21857,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21871,12 +21872,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -21887,10 +21888,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135357739</v>
+        <v>135359836</v>
       </c>
       <c r="B192" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21898,40 +21899,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>655599</v>
+        <v>655835</v>
       </c>
       <c r="R192" t="n">
-        <v>7330842</v>
+        <v>7330823</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21960,7 +21958,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21970,7 +21968,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21979,19 +21977,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -22002,7 +21999,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135359830</v>
+        <v>135357739</v>
       </c>
       <c r="B193" t="n">
         <v>83358</v>
@@ -22031,16 +22028,19 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>655798</v>
+        <v>655599</v>
       </c>
       <c r="R193" t="n">
-        <v>7330738</v>
+        <v>7330842</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22072,7 +22072,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22091,18 +22091,19 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -22113,7 +22114,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135359831</v>
+        <v>135359830</v>
       </c>
       <c r="B194" t="n">
         <v>83358</v>
@@ -22148,10 +22149,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>655805</v>
+        <v>655798</v>
       </c>
       <c r="R194" t="n">
-        <v>7330737</v>
+        <v>7330738</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22224,48 +22225,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135357746</v>
+        <v>135359831</v>
       </c>
       <c r="B195" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>655726</v>
+        <v>655805</v>
       </c>
       <c r="R195" t="n">
-        <v>7330840</v>
+        <v>7330737</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22294,7 +22295,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22304,7 +22305,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22319,12 +22320,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -22335,7 +22336,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135357748</v>
+        <v>135357746</v>
       </c>
       <c r="B196" t="n">
         <v>80493</v>
@@ -22370,13 +22371,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>655719</v>
+        <v>655726</v>
       </c>
       <c r="R196" t="n">
-        <v>7330846</v>
+        <v>7330840</v>
       </c>
       <c r="S196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22405,7 +22406,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22415,7 +22416,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22446,7 +22447,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135359842</v>
+        <v>135357748</v>
       </c>
       <c r="B197" t="n">
         <v>80493</v>
@@ -22477,17 +22478,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>655720</v>
+        <v>655719</v>
       </c>
       <c r="R197" t="n">
-        <v>7330841</v>
+        <v>7330846</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22516,7 +22517,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22526,7 +22527,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22541,12 +22542,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -22557,7 +22558,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135359846</v>
+        <v>135359842</v>
       </c>
       <c r="B198" t="n">
         <v>80493</v>
@@ -22592,10 +22593,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>655723</v>
+        <v>655720</v>
       </c>
       <c r="R198" t="n">
-        <v>7330846</v>
+        <v>7330841</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22627,7 +22628,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22637,7 +22638,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22668,10 +22669,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135357747</v>
+        <v>135359846</v>
       </c>
       <c r="B199" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22679,34 +22680,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>655731</v>
+        <v>655723</v>
       </c>
       <c r="R199" t="n">
-        <v>7330836</v>
+        <v>7330846</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22738,7 +22739,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22748,7 +22749,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22763,12 +22764,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -22779,7 +22780,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135359841</v>
+        <v>135357747</v>
       </c>
       <c r="B200" t="n">
         <v>80499</v>
@@ -22810,17 +22811,17 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>655722</v>
+        <v>655731</v>
       </c>
       <c r="R200" t="n">
-        <v>7330844</v>
+        <v>7330836</v>
       </c>
       <c r="S200" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22849,7 +22850,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22859,7 +22860,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22874,12 +22875,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -22890,7 +22891,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135359845</v>
+        <v>135359841</v>
       </c>
       <c r="B201" t="n">
         <v>80499</v>
@@ -22925,13 +22926,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>655723</v>
+        <v>655722</v>
       </c>
       <c r="R201" t="n">
-        <v>7330845</v>
+        <v>7330844</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22960,7 +22961,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22970,7 +22971,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23001,10 +23002,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135359843</v>
+        <v>135359845</v>
       </c>
       <c r="B202" t="n">
-        <v>80500</v>
+        <v>80499</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23012,21 +23013,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23039,7 +23040,7 @@
         <v>655723</v>
       </c>
       <c r="R202" t="n">
-        <v>7330841</v>
+        <v>7330845</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23071,7 +23072,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23081,7 +23082,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23112,7 +23113,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135359847</v>
+        <v>135359843</v>
       </c>
       <c r="B203" t="n">
         <v>80500</v>
@@ -23150,7 +23151,7 @@
         <v>655723</v>
       </c>
       <c r="R203" t="n">
-        <v>7330846</v>
+        <v>7330841</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23182,7 +23183,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -23192,7 +23193,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23223,53 +23224,48 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135313442</v>
+        <v>135359847</v>
       </c>
       <c r="B204" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>655548</v>
+        <v>655723</v>
       </c>
       <c r="R204" t="n">
-        <v>7330875</v>
+        <v>7330846</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23293,12 +23289,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23313,19 +23319,23 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr"/>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135357407</v>
+        <v>135313442</v>
       </c>
       <c r="B205" t="n">
         <v>57975</v>
@@ -23354,19 +23364,24 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna, Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>655446</v>
+        <v>655548</v>
       </c>
       <c r="R205" t="n">
-        <v>7330950</v>
+        <v>7330875</v>
       </c>
       <c r="S205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23390,27 +23405,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23425,23 +23425,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135357742</v>
+        <v>135357407</v>
       </c>
       <c r="B206" t="n">
         <v>57975</v>
@@ -23472,17 +23468,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Bergmyrarna_topo, Pi lm</t>
+          <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>655598</v>
+        <v>655446</v>
       </c>
       <c r="R206" t="n">
-        <v>7330813</v>
+        <v>7330950</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23511,7 +23507,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23521,12 +23517,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Ringhack, äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23541,12 +23537,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -23557,7 +23553,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135357749</v>
+        <v>135357742</v>
       </c>
       <c r="B207" t="n">
         <v>57975</v>
@@ -23592,10 +23588,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>655721</v>
+        <v>655598</v>
       </c>
       <c r="R207" t="n">
-        <v>7330844</v>
+        <v>7330813</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23627,7 +23623,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23637,7 +23633,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -23673,7 +23669,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>135357861</v>
+        <v>135357749</v>
       </c>
       <c r="B208" t="n">
         <v>57975</v>
@@ -23702,24 +23698,19 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Bergmyrarna, Pi lm</t>
+          <t>Bergmyrarna_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>655427</v>
+        <v>655721</v>
       </c>
       <c r="R208" t="n">
-        <v>7330867</v>
+        <v>7330844</v>
       </c>
       <c r="S208" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23748,7 +23739,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23758,12 +23749,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23778,19 +23769,23 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135357863</v>
+        <v>135357861</v>
       </c>
       <c r="B209" t="n">
         <v>57975</v>
@@ -23830,10 +23825,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>655432</v>
+        <v>655427</v>
       </c>
       <c r="R209" t="n">
-        <v>7330859</v>
+        <v>7330867</v>
       </c>
       <c r="S209" t="n">
         <v>3</v>
@@ -23865,7 +23860,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23875,7 +23870,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -23907,7 +23902,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135357864</v>
+        <v>135357863</v>
       </c>
       <c r="B210" t="n">
         <v>57975</v>
@@ -23947,10 +23942,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>655443</v>
+        <v>655432</v>
       </c>
       <c r="R210" t="n">
-        <v>7330856</v>
+        <v>7330859</v>
       </c>
       <c r="S210" t="n">
         <v>3</v>
@@ -23982,7 +23977,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23992,7 +23987,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -24024,7 +24019,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135357865</v>
+        <v>135357864</v>
       </c>
       <c r="B211" t="n">
         <v>57975</v>
@@ -24064,10 +24059,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>655447</v>
+        <v>655443</v>
       </c>
       <c r="R211" t="n">
-        <v>7330838</v>
+        <v>7330856</v>
       </c>
       <c r="S211" t="n">
         <v>3</v>
@@ -24099,7 +24094,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24109,7 +24104,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -24141,7 +24136,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135357869</v>
+        <v>135357865</v>
       </c>
       <c r="B212" t="n">
         <v>57975</v>
@@ -24172,7 +24167,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -24181,10 +24176,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>655554</v>
+        <v>655447</v>
       </c>
       <c r="R212" t="n">
-        <v>7330873</v>
+        <v>7330838</v>
       </c>
       <c r="S212" t="n">
         <v>3</v>
@@ -24216,7 +24211,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -24226,12 +24221,12 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24258,7 +24253,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135357879</v>
+        <v>135357869</v>
       </c>
       <c r="B213" t="n">
         <v>57975</v>
@@ -24289,7 +24284,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -24298,10 +24293,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>655572</v>
+        <v>655554</v>
       </c>
       <c r="R213" t="n">
-        <v>7330861</v>
+        <v>7330873</v>
       </c>
       <c r="S213" t="n">
         <v>3</v>
@@ -24333,7 +24328,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -24343,12 +24338,12 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24375,7 +24370,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135357885</v>
+        <v>135357879</v>
       </c>
       <c r="B214" t="n">
         <v>57975</v>
@@ -24406,7 +24401,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24415,10 +24410,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>655629</v>
+        <v>655572</v>
       </c>
       <c r="R214" t="n">
-        <v>7330853</v>
+        <v>7330861</v>
       </c>
       <c r="S214" t="n">
         <v>3</v>
@@ -24450,7 +24445,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24460,12 +24455,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24492,7 +24487,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135357894</v>
+        <v>135357885</v>
       </c>
       <c r="B215" t="n">
         <v>57975</v>
@@ -24532,10 +24527,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>655779</v>
+        <v>655629</v>
       </c>
       <c r="R215" t="n">
-        <v>7330760</v>
+        <v>7330853</v>
       </c>
       <c r="S215" t="n">
         <v>3</v>
@@ -24567,7 +24562,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24577,12 +24572,12 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Medelhög livsmiljövärde</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24609,7 +24604,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135357902</v>
+        <v>135357894</v>
       </c>
       <c r="B216" t="n">
         <v>57975</v>
@@ -24640,7 +24635,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24649,10 +24644,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>655610</v>
+        <v>655779</v>
       </c>
       <c r="R216" t="n">
-        <v>7330878</v>
+        <v>7330760</v>
       </c>
       <c r="S216" t="n">
         <v>3</v>
@@ -24684,7 +24679,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -24694,12 +24689,12 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Medelhög livsmiljövärde</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24726,7 +24721,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135357906</v>
+        <v>135357902</v>
       </c>
       <c r="B217" t="n">
         <v>57975</v>
@@ -24766,10 +24761,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>655510</v>
+        <v>655610</v>
       </c>
       <c r="R217" t="n">
-        <v>7330908</v>
+        <v>7330878</v>
       </c>
       <c r="S217" t="n">
         <v>3</v>
@@ -24801,7 +24796,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24811,7 +24806,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -24843,7 +24838,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135359803</v>
+        <v>135357906</v>
       </c>
       <c r="B218" t="n">
         <v>57975</v>
@@ -24872,19 +24867,24 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>655451</v>
+        <v>655510</v>
       </c>
       <c r="R218" t="n">
-        <v>7330842</v>
+        <v>7330908</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24923,12 +24923,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24943,23 +24943,19 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY218" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135362057</v>
+        <v>135359803</v>
       </c>
       <c r="B219" t="n">
         <v>57975</v>
@@ -24988,24 +24984,16 @@
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>655531</v>
+        <v>655451</v>
       </c>
       <c r="R219" t="n">
-        <v>7331104</v>
+        <v>7330842</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -25037,7 +25025,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25047,7 +25035,12 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25062,12 +25055,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -25078,7 +25071,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135362059</v>
+        <v>135362057</v>
       </c>
       <c r="B220" t="n">
         <v>57975</v>
@@ -25121,10 +25114,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>655629</v>
+        <v>655531</v>
       </c>
       <c r="R220" t="n">
-        <v>7331036</v>
+        <v>7331104</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -25156,7 +25149,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25166,7 +25159,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25197,7 +25190,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135362064</v>
+        <v>135362059</v>
       </c>
       <c r="B221" t="n">
         <v>57975</v>
@@ -25240,13 +25233,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>655445</v>
+        <v>655629</v>
       </c>
       <c r="R221" t="n">
-        <v>7331056</v>
+        <v>7331036</v>
       </c>
       <c r="S221" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25275,7 +25268,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25285,7 +25278,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25316,64 +25309,56 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135357903</v>
+        <v>135362064</v>
       </c>
       <c r="B222" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>655565</v>
+        <v>655445</v>
       </c>
       <c r="R222" t="n">
-        <v>7330914</v>
+        <v>7331056</v>
       </c>
       <c r="S222" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25402,7 +25387,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25412,7 +25397,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25427,22 +25412,26 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135359824</v>
+        <v>135357903</v>
       </c>
       <c r="B223" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25450,37 +25439,53 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>655631</v>
+        <v>655565</v>
       </c>
       <c r="R223" t="n">
-        <v>7330798</v>
+        <v>7330914</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25509,7 +25514,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25519,7 +25524,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25534,48 +25539,44 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY223" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135359839</v>
+        <v>135359824</v>
       </c>
       <c r="B224" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25585,10 +25586,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>655777</v>
+        <v>655631</v>
       </c>
       <c r="R224" t="n">
-        <v>7330820</v>
+        <v>7330798</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -25620,7 +25621,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25630,7 +25631,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25661,32 +25662,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135363827</v>
+        <v>135359839</v>
       </c>
       <c r="B225" t="n">
-        <v>99197</v>
+        <v>58136</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>219811</v>
+        <v>103021</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25696,7 +25697,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>655525</v>
+        <v>655777</v>
       </c>
       <c r="R225" t="n">
         <v>7330820</v>
@@ -25731,7 +25732,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25741,7 +25742,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25756,12 +25757,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -25772,10 +25773,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135357398</v>
+        <v>135363827</v>
       </c>
       <c r="B226" t="n">
-        <v>99099</v>
+        <v>99197</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25783,21 +25784,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25807,10 +25808,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>655579</v>
+        <v>655525</v>
       </c>
       <c r="R226" t="n">
-        <v>7330863</v>
+        <v>7330820</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -25842,7 +25843,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25852,7 +25853,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25867,12 +25868,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -25883,7 +25884,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135357400</v>
+        <v>135357398</v>
       </c>
       <c r="B227" t="n">
         <v>99099</v>
@@ -25918,13 +25919,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R227" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25953,7 +25954,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25963,7 +25964,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25994,7 +25995,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135359822</v>
+        <v>135357400</v>
       </c>
       <c r="B228" t="n">
         <v>99099</v>
@@ -26029,13 +26030,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>655610</v>
+        <v>655621</v>
       </c>
       <c r="R228" t="n">
-        <v>7330795</v>
+        <v>7330834</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26064,7 +26065,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26074,7 +26075,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26089,12 +26090,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26105,10 +26106,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135357395</v>
+        <v>135359822</v>
       </c>
       <c r="B229" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26116,21 +26117,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26140,13 +26141,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>655546</v>
+        <v>655610</v>
       </c>
       <c r="R229" t="n">
-        <v>7330858</v>
+        <v>7330795</v>
       </c>
       <c r="S229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26175,7 +26176,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26185,7 +26186,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26200,12 +26201,12 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -26216,7 +26217,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135357397</v>
+        <v>135357395</v>
       </c>
       <c r="B230" t="n">
         <v>99217</v>
@@ -26251,13 +26252,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>655579</v>
+        <v>655546</v>
       </c>
       <c r="R230" t="n">
-        <v>7330863</v>
+        <v>7330858</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26286,7 +26287,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -26296,7 +26297,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26327,7 +26328,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135357399</v>
+        <v>135357397</v>
       </c>
       <c r="B231" t="n">
         <v>99217</v>
@@ -26362,13 +26363,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>655621</v>
+        <v>655579</v>
       </c>
       <c r="R231" t="n">
-        <v>7330834</v>
+        <v>7330863</v>
       </c>
       <c r="S231" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26397,7 +26398,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26407,7 +26408,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26438,7 +26439,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135357401</v>
+        <v>135357399</v>
       </c>
       <c r="B232" t="n">
         <v>99217</v>
@@ -26473,13 +26474,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>655806</v>
+        <v>655621</v>
       </c>
       <c r="R232" t="n">
-        <v>7330742</v>
+        <v>7330834</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26508,7 +26509,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26518,7 +26519,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26549,7 +26550,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135357402</v>
+        <v>135357401</v>
       </c>
       <c r="B233" t="n">
         <v>99217</v>
@@ -26584,10 +26585,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>655842</v>
+        <v>655806</v>
       </c>
       <c r="R233" t="n">
-        <v>7330740</v>
+        <v>7330742</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -26619,7 +26620,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26629,7 +26630,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26660,7 +26661,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135357403</v>
+        <v>135357402</v>
       </c>
       <c r="B234" t="n">
         <v>99217</v>
@@ -26695,10 +26696,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>655735</v>
+        <v>655842</v>
       </c>
       <c r="R234" t="n">
-        <v>7330853</v>
+        <v>7330740</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -26730,7 +26731,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26740,7 +26741,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26771,7 +26772,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135357405</v>
+        <v>135357403</v>
       </c>
       <c r="B235" t="n">
         <v>99217</v>
@@ -26806,13 +26807,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>655649</v>
+        <v>655735</v>
       </c>
       <c r="R235" t="n">
-        <v>7330872</v>
+        <v>7330853</v>
       </c>
       <c r="S235" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26841,7 +26842,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26851,7 +26852,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26882,7 +26883,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135357406</v>
+        <v>135357405</v>
       </c>
       <c r="B236" t="n">
         <v>99217</v>
@@ -26917,13 +26918,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>655448</v>
+        <v>655649</v>
       </c>
       <c r="R236" t="n">
-        <v>7330951</v>
+        <v>7330872</v>
       </c>
       <c r="S236" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26952,7 +26953,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26962,7 +26963,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26993,7 +26994,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135359811</v>
+        <v>135357406</v>
       </c>
       <c r="B237" t="n">
         <v>99217</v>
@@ -27028,13 +27029,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>655554</v>
+        <v>655448</v>
       </c>
       <c r="R237" t="n">
-        <v>7330834</v>
+        <v>7330951</v>
       </c>
       <c r="S237" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -27063,7 +27064,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27073,12 +27074,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27093,12 +27089,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27109,7 +27105,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135359812</v>
+        <v>135359811</v>
       </c>
       <c r="B238" t="n">
         <v>99217</v>
@@ -27144,13 +27140,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>655568</v>
+        <v>655554</v>
       </c>
       <c r="R238" t="n">
-        <v>7330829</v>
+        <v>7330834</v>
       </c>
       <c r="S238" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27179,7 +27175,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27189,12 +27185,12 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>4 exemplar</t>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27225,7 +27221,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135359813</v>
+        <v>135359812</v>
       </c>
       <c r="B239" t="n">
         <v>99217</v>
@@ -27260,13 +27256,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>655571</v>
+        <v>655568</v>
       </c>
       <c r="R239" t="n">
-        <v>7330837</v>
+        <v>7330829</v>
       </c>
       <c r="S239" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27295,7 +27291,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27305,12 +27301,12 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>4 exemplar</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27341,7 +27337,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135359821</v>
+        <v>135359813</v>
       </c>
       <c r="B240" t="n">
         <v>99217</v>
@@ -27376,13 +27372,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>655613</v>
+        <v>655571</v>
       </c>
       <c r="R240" t="n">
-        <v>7330794</v>
+        <v>7330837</v>
       </c>
       <c r="S240" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27411,7 +27407,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27421,7 +27417,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -27457,7 +27453,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135359838</v>
+        <v>135359821</v>
       </c>
       <c r="B241" t="n">
         <v>99217</v>
@@ -27492,10 +27488,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>655778</v>
+        <v>655613</v>
       </c>
       <c r="R241" t="n">
-        <v>7330823</v>
+        <v>7330794</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -27527,7 +27523,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27537,7 +27533,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr">
@@ -27573,7 +27569,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135359851</v>
+        <v>135359838</v>
       </c>
       <c r="B242" t="n">
         <v>99217</v>
@@ -27608,13 +27604,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>655429</v>
+        <v>655778</v>
       </c>
       <c r="R242" t="n">
-        <v>7330949</v>
+        <v>7330823</v>
       </c>
       <c r="S242" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27643,7 +27639,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27653,7 +27649,12 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27684,7 +27685,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135363823</v>
+        <v>135359851</v>
       </c>
       <c r="B243" t="n">
         <v>99217</v>
@@ -27719,13 +27720,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>655537</v>
+        <v>655429</v>
       </c>
       <c r="R243" t="n">
-        <v>7330838</v>
+        <v>7330949</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27754,7 +27755,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27764,7 +27765,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27779,12 +27780,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -27795,32 +27796,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135357608</v>
+        <v>135363823</v>
       </c>
       <c r="B244" t="n">
-        <v>79452</v>
+        <v>99217</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>864</v>
+        <v>221952</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27830,10 +27831,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>655448</v>
+        <v>655537</v>
       </c>
       <c r="R244" t="n">
-        <v>7331407</v>
+        <v>7330838</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -27865,7 +27866,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27875,12 +27876,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27895,12 +27891,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27911,7 +27907,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135362050</v>
+        <v>135357608</v>
       </c>
       <c r="B245" t="n">
         <v>79452</v>
@@ -27946,10 +27942,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>655450</v>
+        <v>655448</v>
       </c>
       <c r="R245" t="n">
-        <v>7331353</v>
+        <v>7331407</v>
       </c>
       <c r="S245" t="n">
         <v>5</v>
@@ -27981,7 +27977,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27991,7 +27987,12 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28006,12 +28007,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -28022,7 +28023,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135362051</v>
+        <v>135362050</v>
       </c>
       <c r="B246" t="n">
         <v>79452</v>
@@ -28057,13 +28058,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>655435</v>
+        <v>655450</v>
       </c>
       <c r="R246" t="n">
-        <v>7331358</v>
+        <v>7331353</v>
       </c>
       <c r="S246" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -28092,7 +28093,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28102,7 +28103,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28111,7 +28112,6 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -28134,32 +28134,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135357607</v>
+        <v>135362051</v>
       </c>
       <c r="B247" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28169,13 +28169,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>655444</v>
+        <v>655435</v>
       </c>
       <c r="R247" t="n">
-        <v>7331409</v>
+        <v>7331358</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28214,12 +28214,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28228,18 +28223,19 @@
       <c r="AE247" t="b">
         <v>0</v>
       </c>
+      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -28250,7 +28246,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135357609</v>
+        <v>135357607</v>
       </c>
       <c r="B248" t="n">
         <v>79373</v>
@@ -28285,13 +28281,13 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>655447</v>
+        <v>655444</v>
       </c>
       <c r="R248" t="n">
-        <v>7331408</v>
+        <v>7331409</v>
       </c>
       <c r="S248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28320,7 +28316,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28330,7 +28326,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28361,7 +28362,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135357610</v>
+        <v>135357609</v>
       </c>
       <c r="B249" t="n">
         <v>79373</v>
@@ -28396,13 +28397,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>655445</v>
+        <v>655447</v>
       </c>
       <c r="R249" t="n">
-        <v>7331409</v>
+        <v>7331408</v>
       </c>
       <c r="S249" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28472,7 +28473,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135357613</v>
+        <v>135357610</v>
       </c>
       <c r="B250" t="n">
         <v>79373</v>
@@ -28507,13 +28508,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>655422</v>
+        <v>655445</v>
       </c>
       <c r="R250" t="n">
-        <v>7331225</v>
+        <v>7331409</v>
       </c>
       <c r="S250" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28542,7 +28543,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28552,7 +28553,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28583,7 +28584,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135357614</v>
+        <v>135357613</v>
       </c>
       <c r="B251" t="n">
         <v>79373</v>
@@ -28621,10 +28622,10 @@
         <v>655422</v>
       </c>
       <c r="R251" t="n">
-        <v>7331227</v>
+        <v>7331225</v>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28653,7 +28654,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28663,7 +28664,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28694,7 +28695,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135357615</v>
+        <v>135357614</v>
       </c>
       <c r="B252" t="n">
         <v>79373</v>
@@ -28729,13 +28730,13 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>655423</v>
+        <v>655422</v>
       </c>
       <c r="R252" t="n">
-        <v>7331217</v>
+        <v>7331227</v>
       </c>
       <c r="S252" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28764,7 +28765,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28774,7 +28775,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28805,7 +28806,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135362056</v>
+        <v>135357615</v>
       </c>
       <c r="B253" t="n">
         <v>79373</v>
@@ -28840,13 +28841,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>655425</v>
+        <v>655423</v>
       </c>
       <c r="R253" t="n">
-        <v>7331260</v>
+        <v>7331217</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28875,7 +28876,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28885,7 +28886,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28900,12 +28901,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28916,56 +28917,48 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135362049</v>
+        <v>135362056</v>
       </c>
       <c r="B254" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>655450</v>
+        <v>655425</v>
       </c>
       <c r="R254" t="n">
-        <v>7331381</v>
+        <v>7331260</v>
       </c>
       <c r="S254" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28994,7 +28987,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -29004,7 +28997,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29028,6 +29021,125 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>135362049</v>
+      </c>
+      <c r="B255" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Bergmyrarna, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>655450</v>
+      </c>
+      <c r="R255" t="n">
+        <v>7331381</v>
+      </c>
+      <c r="S255" t="n">
+        <v>5</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -12591,11 +12591,14 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bergmyrarna, Pi lm</t>
@@ -12670,7 +12673,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AZ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356802</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356803</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357587</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357591</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357630</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1788,6 +1838,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357852</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358259</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362040</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357856</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2218,6 +2288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357389</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2329,6 +2404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359785</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2440,6 +2520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359788</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359798</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2662,6 +2752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359852</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2773,6 +2868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356789</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2884,6 +2984,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356791</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2995,6 +3100,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356793</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3106,6 +3216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356798</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3217,6 +3332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356801</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356804</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3439,6 +3564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356805</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3550,6 +3680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356806</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3661,6 +3796,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356807</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3772,6 +3912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356808</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3883,6 +4028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357388</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3994,6 +4144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357392</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4105,6 +4260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357394</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4221,6 +4381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357576</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4332,6 +4497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357577</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4443,6 +4613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357580</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4554,6 +4729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357581</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4665,6 +4845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357583</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4776,6 +4961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357584</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4887,6 +5077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357586</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4998,6 +5193,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357589</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5109,6 +5309,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357590</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5220,6 +5425,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357592</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5331,6 +5541,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357594</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5442,6 +5657,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357595</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5553,6 +5773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357617</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5664,6 +5889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357618</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5775,6 +6005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357622</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5886,6 +6121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357623</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5997,6 +6237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357624</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6108,6 +6353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357625</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6219,6 +6469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357627</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6330,6 +6585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357628</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6441,6 +6701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357631</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6548,6 +6813,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357853</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6655,6 +6925,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357854</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6756,6 +7031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358263</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6872,6 +7152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359086</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6988,6 +7273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359087</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7104,6 +7394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359088</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7220,6 +7515,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359089</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7336,6 +7636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359090</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7452,6 +7757,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359091</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7568,6 +7878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359092</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7684,6 +7999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359093</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7800,6 +8120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359095</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7914,6 +8239,11 @@
       <c r="AY66" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359097</t>
         </is>
       </c>
     </row>
@@ -8031,6 +8361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359781</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8142,6 +8477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359787</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8253,6 +8593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359789</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8365,6 +8710,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359793</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8476,6 +8826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359795</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8587,6 +8942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359796</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8698,6 +9058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359797</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8809,6 +9174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359799</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8920,6 +9290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362032</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9031,6 +9406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362033</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9142,6 +9522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362036</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9253,6 +9638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362038</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9364,6 +9754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362039</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9475,6 +9870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362044</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9586,6 +9986,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362047</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9697,6 +10102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362066</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9808,6 +10218,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357733</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9919,6 +10334,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357735</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10030,6 +10450,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356790</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10141,6 +10566,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356797</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10252,6 +10682,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356800</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10368,6 +10803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359085</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10484,6 +10924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359098</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10595,6 +11040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362041</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10711,6 +11161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359096</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10827,6 +11282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359853</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10946,6 +11406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362037</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11048,6 +11513,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313304</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11164,6 +11634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357579</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11280,6 +11755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357588</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11396,6 +11876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357626</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11512,6 +11997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357734</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11629,6 +12119,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357857</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11735,6 +12230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358260</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11851,6 +12351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359094</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11967,6 +12472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359100</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12083,6 +12593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359784</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12202,6 +12717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362035</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12321,6 +12841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362042</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12440,6 +12965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362043</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12559,6 +13089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362065</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12678,6 +13213,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135519109</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12794,6 +13334,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359099</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12925,6 +13470,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363819</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13036,6 +13586,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356795</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13167,6 +13722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363820</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13278,6 +13838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359792</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13389,6 +13954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357600</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13500,6 +14070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357596</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13611,6 +14186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357598</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13722,6 +14302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357601</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13833,6 +14418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357604</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13944,6 +14534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357605</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14055,6 +14650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357612</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14166,6 +14766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357616</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14267,6 +14872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358261</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14378,6 +14988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362048</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14489,6 +15104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362055</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14598,6 +15218,11 @@
       <c r="AY125" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362052</t>
         </is>
       </c>
     </row>
@@ -14715,6 +15340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362054</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14829,6 +15459,11 @@
       <c r="AY127" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357743</t>
         </is>
       </c>
     </row>
@@ -14946,6 +15581,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357753</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15058,6 +15698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359820</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15165,6 +15810,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357874</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15280,6 +15930,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357745</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15397,6 +16052,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313461</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15498,6 +16158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358264</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15614,6 +16279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359833</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15725,6 +16395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362060</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15836,6 +16511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362061</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15943,6 +16623,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357881</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16067,6 +16752,11 @@
       <c r="AY138" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363826</t>
         </is>
       </c>
     </row>
@@ -16184,6 +16874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357752</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16291,6 +16986,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357859</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16398,6 +17098,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357873</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16505,6 +17210,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357875</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16612,6 +17322,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357882</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16719,6 +17434,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357898</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16828,6 +17548,11 @@
       <c r="AY145" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359825</t>
         </is>
       </c>
     </row>
@@ -16950,6 +17675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357751</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17061,6 +17791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359815</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17172,6 +17907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359817</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17283,6 +18023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359819</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17394,6 +18139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359834</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17505,6 +18255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359835</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17616,6 +18371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359848</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17728,6 +18488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357396</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17837,6 +18602,11 @@
       <c r="AY154" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359850</t>
         </is>
       </c>
     </row>
@@ -17954,6 +18724,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388328</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18051,6 +18826,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313467</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18162,6 +18942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357404</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18273,6 +19058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357620</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18384,6 +19174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357621</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18495,6 +19290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357736</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18606,6 +19406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357737</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18717,6 +19522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357740</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18828,6 +19638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357750</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18935,6 +19750,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357858</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19047,6 +19867,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357866</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19159,6 +19984,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357867</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19266,6 +20096,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357872</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19373,6 +20208,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357878</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19480,6 +20320,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357883</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19587,6 +20432,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357896</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19694,6 +20544,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357897</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19801,6 +20656,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357899</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19908,6 +20768,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357900</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20015,6 +20880,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357901</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20116,6 +20986,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358262</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20227,6 +21102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359801</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20338,6 +21218,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359804</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20449,6 +21334,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359805</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20560,6 +21450,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359809</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20671,6 +21566,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359810</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20782,6 +21682,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359816</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20893,6 +21798,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359818</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21004,6 +21914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359823</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21115,6 +22030,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359829</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21226,6 +22146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359832</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21337,6 +22262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359837</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21448,6 +22378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359849</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21559,6 +22494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362058</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21670,6 +22610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362062</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21781,6 +22726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362063</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21892,6 +22842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363825</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22001,6 +22956,11 @@
       <c r="AY192" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359836</t>
         </is>
       </c>
     </row>
@@ -22118,6 +23078,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357739</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22229,6 +23194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359830</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22340,6 +23310,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359831</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22451,6 +23426,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357746</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22562,6 +23542,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357748</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22673,6 +23658,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359842</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22784,6 +23774,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359846</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22895,6 +23890,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357747</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23006,6 +24006,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359841</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23117,6 +24122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359845</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23228,6 +24238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359843</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23339,6 +24354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359847</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23441,6 +24461,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313442</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23557,6 +24582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357407</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23673,6 +24703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357742</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23789,6 +24824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357749</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23906,6 +24946,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357861</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24023,6 +25068,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357863</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24140,6 +25190,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357864</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24257,6 +25312,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357865</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24374,6 +25434,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357869</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24491,6 +25556,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357879</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24608,6 +25678,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357885</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24725,6 +25800,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357894</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24842,6 +25922,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357902</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24959,6 +26044,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357906</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25075,6 +26165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359803</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25194,6 +26289,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362057</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25313,6 +26413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362059</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25432,6 +26537,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362064</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25555,6 +26665,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357903</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25666,6 +26781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359824</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25777,6 +26897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359839</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25888,6 +27013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363827</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25999,6 +27129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357398</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26110,6 +27245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357400</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26221,6 +27361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359822</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26332,6 +27477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357395</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26443,6 +27593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357397</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26554,6 +27709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357399</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26665,6 +27825,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357401</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26776,6 +27941,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357402</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26887,6 +28057,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357403</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26998,6 +28173,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357405</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27109,6 +28289,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357406</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27225,6 +28410,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359811</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27341,6 +28531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359812</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27457,6 +28652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359813</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27573,6 +28773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359821</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27689,6 +28894,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359838</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27800,6 +29010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359851</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27911,6 +29126,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363823</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28027,6 +29247,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357608</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28138,6 +29363,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362050</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28250,6 +29480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362051</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28366,6 +29601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357607</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28477,6 +29717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357609</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28588,6 +29833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357610</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28699,6 +29949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357613</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28810,6 +30065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357614</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28921,6 +30181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357615</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29032,6 +30297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362056</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29151,8 +30421,269 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362049</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357390</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135356799</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135356794</v>
       </c>
       <c r="B4" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135356802</v>
       </c>
       <c r="B5" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135356803</v>
       </c>
       <c r="B6" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135357582</v>
       </c>
       <c r="B7" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135357587</v>
       </c>
       <c r="B8" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135357591</v>
       </c>
       <c r="B9" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135357630</v>
       </c>
       <c r="B10" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135357852</v>
       </c>
       <c r="B11" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>135358259</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135362040</v>
       </c>
       <c r="B13" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135357856</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>135357389</v>
       </c>
       <c r="B15" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135359785</v>
       </c>
       <c r="B16" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135359788</v>
       </c>
       <c r="B17" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>135359798</v>
       </c>
       <c r="B18" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>135359852</v>
       </c>
       <c r="B19" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135356789</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135356791</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>135356793</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>135356798</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>135356801</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135356804</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>135356805</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135356806</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135356807</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135356808</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135357388</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135357392</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135357394</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135357576</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>135357577</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>135357580</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135357581</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>135357583</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>135357584</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>135357586</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>135357589</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>135357590</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>135357592</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>135357594</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>135357595</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135357617</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135357618</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>135357622</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>135357623</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135357624</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>135357625</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>135357627</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>135357628</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>135357631</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135357853</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135357854</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135358263</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135359086</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135359087</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>135359088</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135359089</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>135359090</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>135359091</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135359092</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>135359093</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>135359095</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>135359097</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>135359781</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>135359787</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>135359789</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>135359793</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135359795</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>135359796</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>135359797</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>135359799</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>135362032</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>135362033</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>135362036</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>135362038</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>135362039</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>135362044</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>135362047</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>135362066</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>135357733</v>
       </c>
       <c r="B83" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>135357735</v>
       </c>
       <c r="B84" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>135356790</v>
       </c>
       <c r="B85" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>135356797</v>
       </c>
       <c r="B86" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>135356800</v>
       </c>
       <c r="B87" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135359085</v>
       </c>
       <c r="B88" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>135359098</v>
       </c>
       <c r="B89" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135362041</v>
       </c>
       <c r="B90" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>135359096</v>
       </c>
       <c r="B91" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>135359853</v>
       </c>
       <c r="B92" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>135362037</v>
       </c>
       <c r="B93" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>135313304</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>135357579</v>
       </c>
       <c r="B95" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>135357588</v>
       </c>
       <c r="B96" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>135357626</v>
       </c>
       <c r="B97" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>135357734</v>
       </c>
       <c r="B98" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>135357857</v>
       </c>
       <c r="B99" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>135358260</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>135359094</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>135359100</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>135359784</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>135362035</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>135362042</v>
       </c>
       <c r="B105" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>135362043</v>
       </c>
       <c r="B106" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>135362065</v>
       </c>
       <c r="B107" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135519109</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>135359099</v>
       </c>
       <c r="B109" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>135359792</v>
       </c>
       <c r="B113" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>135357600</v>
       </c>
       <c r="B114" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>135357596</v>
       </c>
       <c r="B115" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>135357598</v>
       </c>
       <c r="B116" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>135357601</v>
       </c>
       <c r="B117" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>135357604</v>
       </c>
       <c r="B118" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>135357605</v>
       </c>
       <c r="B119" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>135357612</v>
       </c>
       <c r="B120" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>135357616</v>
       </c>
       <c r="B121" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>135358261</v>
       </c>
       <c r="B122" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>135362048</v>
       </c>
       <c r="B123" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>135362055</v>
       </c>
       <c r="B124" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>135362052</v>
       </c>
       <c r="B125" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>135362054</v>
       </c>
       <c r="B126" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>135357743</v>
       </c>
       <c r="B127" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>135357753</v>
       </c>
       <c r="B128" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>135359820</v>
       </c>
       <c r="B129" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>135357874</v>
       </c>
       <c r="B130" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>135357745</v>
       </c>
       <c r="B131" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>135313461</v>
       </c>
       <c r="B132" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>135358264</v>
       </c>
       <c r="B133" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>135359833</v>
       </c>
       <c r="B134" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>135362060</v>
       </c>
       <c r="B135" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>135362061</v>
       </c>
       <c r="B136" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>135357881</v>
       </c>
       <c r="B137" t="n">
-        <v>92689</v>
+        <v>92731</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>135363826</v>
       </c>
       <c r="B138" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>135357752</v>
       </c>
       <c r="B139" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>135357859</v>
       </c>
       <c r="B140" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>135357873</v>
       </c>
       <c r="B141" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>135357875</v>
       </c>
       <c r="B142" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>135357882</v>
       </c>
       <c r="B143" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>135357898</v>
       </c>
       <c r="B144" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>135359825</v>
       </c>
       <c r="B145" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>135357751</v>
       </c>
       <c r="B146" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>135359815</v>
       </c>
       <c r="B147" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>135359817</v>
       </c>
       <c r="B148" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>135359819</v>
       </c>
       <c r="B149" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>135359834</v>
       </c>
       <c r="B150" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>135359835</v>
       </c>
       <c r="B151" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>135359848</v>
       </c>
       <c r="B152" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>135357396</v>
       </c>
       <c r="B153" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>135359850</v>
       </c>
       <c r="B154" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>135388328</v>
       </c>
       <c r="B155" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>135313467</v>
       </c>
       <c r="B156" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>135357404</v>
       </c>
       <c r="B157" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>135357620</v>
       </c>
       <c r="B158" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>135357621</v>
       </c>
       <c r="B159" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>135357736</v>
       </c>
       <c r="B160" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>135357737</v>
       </c>
       <c r="B161" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>135357740</v>
       </c>
       <c r="B162" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135357750</v>
       </c>
       <c r="B163" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>135357858</v>
       </c>
       <c r="B164" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>135357866</v>
       </c>
       <c r="B165" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>135357867</v>
       </c>
       <c r="B166" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>135357872</v>
       </c>
       <c r="B167" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>135357878</v>
       </c>
       <c r="B168" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>135357883</v>
       </c>
       <c r="B169" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>135357896</v>
       </c>
       <c r="B170" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>135357897</v>
       </c>
       <c r="B171" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>135357899</v>
       </c>
       <c r="B172" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>135357900</v>
       </c>
       <c r="B173" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>135357901</v>
       </c>
       <c r="B174" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>135358262</v>
       </c>
       <c r="B175" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>135359801</v>
       </c>
       <c r="B176" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>135359804</v>
       </c>
       <c r="B177" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>135359805</v>
       </c>
       <c r="B178" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>135359809</v>
       </c>
       <c r="B179" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>135359810</v>
       </c>
       <c r="B180" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>135359816</v>
       </c>
       <c r="B181" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>135359818</v>
       </c>
       <c r="B182" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>135359823</v>
       </c>
       <c r="B183" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>135359829</v>
       </c>
       <c r="B184" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>135359832</v>
       </c>
       <c r="B185" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>135359837</v>
       </c>
       <c r="B186" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>135359849</v>
       </c>
       <c r="B187" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>135362058</v>
       </c>
       <c r="B188" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>135362062</v>
       </c>
       <c r="B189" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>135362063</v>
       </c>
       <c r="B190" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>135363825</v>
       </c>
       <c r="B191" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>135359836</v>
       </c>
       <c r="B192" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>135357739</v>
       </c>
       <c r="B193" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>135359830</v>
       </c>
       <c r="B194" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>135359831</v>
       </c>
       <c r="B195" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>135357746</v>
       </c>
       <c r="B196" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>135357748</v>
       </c>
       <c r="B197" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>135359842</v>
       </c>
       <c r="B198" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>135359846</v>
       </c>
       <c r="B199" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>135357747</v>
       </c>
       <c r="B200" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>135359841</v>
       </c>
       <c r="B201" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>135359845</v>
       </c>
       <c r="B202" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>135359843</v>
       </c>
       <c r="B203" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>135359847</v>
       </c>
       <c r="B204" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>135313442</v>
       </c>
       <c r="B205" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>135357407</v>
       </c>
       <c r="B206" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>135357742</v>
       </c>
       <c r="B207" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>135357749</v>
       </c>
       <c r="B208" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>135357861</v>
       </c>
       <c r="B209" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>135357863</v>
       </c>
       <c r="B210" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135357864</v>
       </c>
       <c r="B211" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>135357865</v>
       </c>
       <c r="B212" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>135357869</v>
       </c>
       <c r="B213" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>135357879</v>
       </c>
       <c r="B214" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>135357885</v>
       </c>
       <c r="B215" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>135357894</v>
       </c>
       <c r="B216" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>135357902</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>135357906</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>135359803</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>135362057</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>135362059</v>
       </c>
       <c r="B221" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>135362064</v>
       </c>
       <c r="B222" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>135357903</v>
       </c>
       <c r="B223" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>135359839</v>
       </c>
       <c r="B225" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>135363827</v>
       </c>
       <c r="B226" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>135357398</v>
       </c>
       <c r="B227" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>135357400</v>
       </c>
       <c r="B228" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>135359822</v>
       </c>
       <c r="B229" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>135357395</v>
       </c>
       <c r="B230" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>135357397</v>
       </c>
       <c r="B231" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>135357399</v>
       </c>
       <c r="B232" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>135357401</v>
       </c>
       <c r="B233" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>135357402</v>
       </c>
       <c r="B234" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>135357403</v>
       </c>
       <c r="B235" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>135357405</v>
       </c>
       <c r="B236" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>135357406</v>
       </c>
       <c r="B237" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>135359811</v>
       </c>
       <c r="B238" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>135359812</v>
       </c>
       <c r="B239" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>135359813</v>
       </c>
       <c r="B240" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>135359821</v>
       </c>
       <c r="B241" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>135359838</v>
       </c>
       <c r="B242" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>135359851</v>
       </c>
       <c r="B243" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>135363823</v>
       </c>
       <c r="B244" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>135357608</v>
       </c>
       <c r="B245" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>135362050</v>
       </c>
       <c r="B246" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>135362051</v>
       </c>
       <c r="B247" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>135357607</v>
       </c>
       <c r="B248" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>135357609</v>
       </c>
       <c r="B249" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>135357610</v>
       </c>
       <c r="B250" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>135357613</v>
       </c>
       <c r="B251" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>135357614</v>
       </c>
       <c r="B252" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>135357615</v>
       </c>
       <c r="B253" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>135362056</v>
       </c>
       <c r="B254" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>135362049</v>
       </c>
       <c r="B255" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357390</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135356799</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135356794</v>
       </c>
       <c r="B4" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135356802</v>
       </c>
       <c r="B5" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135356803</v>
       </c>
       <c r="B6" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135357582</v>
       </c>
       <c r="B7" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135357587</v>
       </c>
       <c r="B8" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135357591</v>
       </c>
       <c r="B9" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135357630</v>
       </c>
       <c r="B10" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135357852</v>
       </c>
       <c r="B11" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>135358259</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135362040</v>
       </c>
       <c r="B13" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135357856</v>
       </c>
       <c r="B14" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>135357389</v>
       </c>
       <c r="B15" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135359785</v>
       </c>
       <c r="B16" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135359788</v>
       </c>
       <c r="B17" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>135359798</v>
       </c>
       <c r="B18" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>135359852</v>
       </c>
       <c r="B19" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135356789</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135356791</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>135356793</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>135356798</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>135356801</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135356804</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>135356805</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135356806</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135356807</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135356808</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135357388</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135357392</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135357394</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135357576</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>135357577</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>135357580</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>135357581</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>135357583</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>135357584</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>135357586</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>135357589</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>135357590</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>135357592</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>135357594</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>135357595</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135357617</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>135357618</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>135357622</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>135357623</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135357624</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>135357625</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>135357627</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>135357628</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>135357631</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>135357853</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>135357854</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135358263</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>135359086</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135359087</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>135359088</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135359089</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>135359090</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>135359091</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>135359092</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>135359093</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>135359095</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>135359097</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>135359781</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>135359787</v>
       </c>
       <c r="B68" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>135359789</v>
       </c>
       <c r="B69" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>135359793</v>
       </c>
       <c r="B70" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135359795</v>
       </c>
       <c r="B71" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>135359796</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>135359797</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>135359799</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>135362032</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>135362033</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>135362036</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>135362038</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>135362039</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>135362044</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>135362047</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>135362066</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>135357733</v>
       </c>
       <c r="B83" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>135357735</v>
       </c>
       <c r="B84" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>135356790</v>
       </c>
       <c r="B85" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>135356797</v>
       </c>
       <c r="B86" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>135356800</v>
       </c>
       <c r="B87" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135359085</v>
       </c>
       <c r="B88" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>135359098</v>
       </c>
       <c r="B89" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135362041</v>
       </c>
       <c r="B90" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>135357600</v>
       </c>
       <c r="B114" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>135357596</v>
       </c>
       <c r="B115" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>135357598</v>
       </c>
       <c r="B116" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>135357601</v>
       </c>
       <c r="B117" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>135357604</v>
       </c>
       <c r="B118" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>135357605</v>
       </c>
       <c r="B119" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>135357612</v>
       </c>
       <c r="B120" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>135357616</v>
       </c>
       <c r="B121" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>135358261</v>
       </c>
       <c r="B122" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>135362048</v>
       </c>
       <c r="B123" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>135362055</v>
       </c>
       <c r="B124" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>135362052</v>
       </c>
       <c r="B125" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>135357743</v>
       </c>
       <c r="B127" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>135357753</v>
       </c>
       <c r="B128" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>135359820</v>
       </c>
       <c r="B129" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>135357874</v>
       </c>
       <c r="B130" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>135357745</v>
       </c>
       <c r="B131" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>135313461</v>
       </c>
       <c r="B132" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>135358264</v>
       </c>
       <c r="B133" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>135359833</v>
       </c>
       <c r="B134" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>135362060</v>
       </c>
       <c r="B135" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>135362061</v>
       </c>
       <c r="B136" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>135357881</v>
       </c>
       <c r="B137" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>135363826</v>
       </c>
       <c r="B138" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>135357752</v>
       </c>
       <c r="B139" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>135357859</v>
       </c>
       <c r="B140" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>135357873</v>
       </c>
       <c r="B141" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>135357875</v>
       </c>
       <c r="B142" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>135357882</v>
       </c>
       <c r="B143" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>135357898</v>
       </c>
       <c r="B144" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>135359825</v>
       </c>
       <c r="B145" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>135357751</v>
       </c>
       <c r="B146" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>135359815</v>
       </c>
       <c r="B147" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>135359817</v>
       </c>
       <c r="B148" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>135359819</v>
       </c>
       <c r="B149" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>135359834</v>
       </c>
       <c r="B150" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>135359835</v>
       </c>
       <c r="B151" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>135359848</v>
       </c>
       <c r="B152" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>135357396</v>
       </c>
       <c r="B153" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>135359850</v>
       </c>
       <c r="B154" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>135388328</v>
       </c>
       <c r="B155" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>135313467</v>
       </c>
       <c r="B156" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>135357404</v>
       </c>
       <c r="B157" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>135357620</v>
       </c>
       <c r="B158" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>135357621</v>
       </c>
       <c r="B159" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>135357736</v>
       </c>
       <c r="B160" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>135357737</v>
       </c>
       <c r="B161" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>135357740</v>
       </c>
       <c r="B162" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>135357750</v>
       </c>
       <c r="B163" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>135357858</v>
       </c>
       <c r="B164" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>135357866</v>
       </c>
       <c r="B165" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>135357867</v>
       </c>
       <c r="B166" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>135357872</v>
       </c>
       <c r="B167" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>135357878</v>
       </c>
       <c r="B168" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>135357883</v>
       </c>
       <c r="B169" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>135357896</v>
       </c>
       <c r="B170" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>135357897</v>
       </c>
       <c r="B171" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>135357899</v>
       </c>
       <c r="B172" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>135357900</v>
       </c>
       <c r="B173" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>135357901</v>
       </c>
       <c r="B174" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>135358262</v>
       </c>
       <c r="B175" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>135359801</v>
       </c>
       <c r="B176" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>135359804</v>
       </c>
       <c r="B177" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>135359805</v>
       </c>
       <c r="B178" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>135359809</v>
       </c>
       <c r="B179" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>135359810</v>
       </c>
       <c r="B180" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>135359816</v>
       </c>
       <c r="B181" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>135359818</v>
       </c>
       <c r="B182" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>135359823</v>
       </c>
       <c r="B183" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>135359829</v>
       </c>
       <c r="B184" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>135359832</v>
       </c>
       <c r="B185" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>135359837</v>
       </c>
       <c r="B186" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>135359849</v>
       </c>
       <c r="B187" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>135362058</v>
       </c>
       <c r="B188" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>135362062</v>
       </c>
       <c r="B189" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>135362063</v>
       </c>
       <c r="B190" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>135363825</v>
       </c>
       <c r="B191" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>135359836</v>
       </c>
       <c r="B192" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>135357739</v>
       </c>
       <c r="B193" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>135359830</v>
       </c>
       <c r="B194" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>135359831</v>
       </c>
       <c r="B195" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>135357746</v>
       </c>
       <c r="B196" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>135357748</v>
       </c>
       <c r="B197" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>135359842</v>
       </c>
       <c r="B198" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>135359846</v>
       </c>
       <c r="B199" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>135357747</v>
       </c>
       <c r="B200" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>135359841</v>
       </c>
       <c r="B201" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>135359845</v>
       </c>
       <c r="B202" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>135359843</v>
       </c>
       <c r="B203" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>135359847</v>
       </c>
       <c r="B204" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>135363827</v>
       </c>
       <c r="B226" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>135357398</v>
       </c>
       <c r="B227" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>135357400</v>
       </c>
       <c r="B228" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>135359822</v>
       </c>
       <c r="B229" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>135357395</v>
       </c>
       <c r="B230" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>135357397</v>
       </c>
       <c r="B231" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>135357399</v>
       </c>
       <c r="B232" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>135357401</v>
       </c>
       <c r="B233" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>135357402</v>
       </c>
       <c r="B234" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>135357403</v>
       </c>
       <c r="B235" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>135357405</v>
       </c>
       <c r="B236" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>135357406</v>
       </c>
       <c r="B237" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>135359811</v>
       </c>
       <c r="B238" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>135359812</v>
       </c>
       <c r="B239" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>135359813</v>
       </c>
       <c r="B240" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>135359821</v>
       </c>
       <c r="B241" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>135359838</v>
       </c>
       <c r="B242" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>135359851</v>
       </c>
       <c r="B243" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>135363823</v>
       </c>
       <c r="B244" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>135357608</v>
       </c>
       <c r="B245" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>135362050</v>
       </c>
       <c r="B246" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>135362051</v>
       </c>
       <c r="B247" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>135357607</v>
       </c>
       <c r="B248" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>135357609</v>
       </c>
       <c r="B249" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>135357610</v>
       </c>
       <c r="B250" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>135357613</v>
       </c>
       <c r="B251" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>135357614</v>
       </c>
       <c r="B252" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>135357615</v>
       </c>
       <c r="B253" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>135362056</v>
       </c>
       <c r="B254" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135357390</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135357856</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>135357743</v>
       </c>
       <c r="B127" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>135357753</v>
       </c>
       <c r="B128" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>135359820</v>
       </c>
       <c r="B129" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>135357874</v>
       </c>
       <c r="B130" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>135357745</v>
       </c>
       <c r="B131" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>135357881</v>
       </c>
       <c r="B137" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>135363826</v>
       </c>
       <c r="B138" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>135357752</v>
       </c>
       <c r="B139" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>135357859</v>
       </c>
       <c r="B140" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>135357873</v>
       </c>
       <c r="B141" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>135357875</v>
       </c>
       <c r="B142" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>135357882</v>
       </c>
       <c r="B143" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>135357898</v>
       </c>
       <c r="B144" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>135359825</v>
       </c>
       <c r="B145" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>135357751</v>
       </c>
       <c r="B146" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>135359815</v>
       </c>
       <c r="B147" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>135359850</v>
       </c>
       <c r="B154" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>135388328</v>
       </c>
       <c r="B155" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>135363827</v>
       </c>
       <c r="B226" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>135357398</v>
       </c>
       <c r="B227" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>135357400</v>
       </c>
       <c r="B228" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>135359822</v>
       </c>
       <c r="B229" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>135357395</v>
       </c>
       <c r="B230" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>135357397</v>
       </c>
       <c r="B231" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>135357399</v>
       </c>
       <c r="B232" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>135357401</v>
       </c>
       <c r="B233" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>135357402</v>
       </c>
       <c r="B234" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>135357403</v>
       </c>
       <c r="B235" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>135357405</v>
       </c>
       <c r="B236" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>135357406</v>
       </c>
       <c r="B237" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>135359811</v>
       </c>
       <c r="B238" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>135359812</v>
       </c>
       <c r="B239" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>135359813</v>
       </c>
       <c r="B240" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>135359821</v>
       </c>
       <c r="B241" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>135359838</v>
       </c>
       <c r="B242" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>135359851</v>
       </c>
       <c r="B243" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>135363823</v>
       </c>
       <c r="B244" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>135362040</v>
       </c>
       <c r="B13" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>135362032</v>
       </c>
       <c r="B75" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>135362037</v>
       </c>
       <c r="B93" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>135362035</v>
       </c>
       <c r="B104" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>135362042</v>
       </c>
       <c r="B105" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>135362043</v>
       </c>
       <c r="B106" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>135362065</v>
       </c>
       <c r="B107" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135519109</v>
       </c>
       <c r="B108" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>135363819</v>
       </c>
       <c r="B110" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>135363820</v>
       </c>
       <c r="B112" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>135362052</v>
       </c>
       <c r="B125" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>135362060</v>
       </c>
       <c r="B135" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>135363826</v>
       </c>
       <c r="B138" t="n">
-        <v>92871</v>
+        <v>92886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>135363825</v>
       </c>
       <c r="B191" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>135362057</v>
       </c>
       <c r="B220" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>135362059</v>
       </c>
       <c r="B221" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>135362064</v>
       </c>
       <c r="B222" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>135363827</v>
       </c>
       <c r="B226" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>135363823</v>
       </c>
       <c r="B244" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>135362050</v>
       </c>
       <c r="B246" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>135362049</v>
       </c>
       <c r="B255" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/Bergmyrarna avvanm artfynd.xlsx
+++ b/artfynd/Bergmyrarna avvanm artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>135362040</v>
       </c>
       <c r="B13" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>135362032</v>
       </c>
       <c r="B75" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>135362052</v>
       </c>
       <c r="B125" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>135362060</v>
       </c>
       <c r="B135" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>135362050</v>
       </c>
       <c r="B246" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
